--- a/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
+++ b/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Dependency Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Market Sizing &amp; EU Revenue" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dependency Analysis'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Market Sizing &amp; EU Revenue'!$A$1:$O$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +60,32 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +158,30 @@
         <bgColor rgb="0000B050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6600"/>
+        <bgColor rgb="00FF6600"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -156,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -214,6 +267,94 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3272,4 +3413,1239 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="55" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AREA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SUB-SEGMENT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GLOBAL MARKET SIZE 2025
+(USD bn)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GLOBAL MARKET SIZE 2026E
+(USD bn)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EU MARKET SIZE 2025
+(USD bn)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>EU MARKET SIZE 2026E
+(USD bn)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>EU AS % OF
+GLOBAL (2025)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>EU AS % OF
+GLOBAL (2026E)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>EU REVENUE CAPTURED BY
+EU-HQ COMPANIES (USD bn, 2025)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EU REVENUE CAPTURED BY
+NON-EU COMPANIES (USD bn, 2025)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>% CAPTURED BY
+EU COMPANIES</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>% CAPTURED BY
+NON-EU COMPANIES</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>KEY EU COMPANIES
+(Revenue, 2025)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>KEY NON-EU COMPANIES
+(Share of EU Market)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE / NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>SEMICONDUCTORS</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Total Semiconductor Market</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="n">
+        <v>791.7</v>
+      </c>
+      <c r="D2" s="20" t="n">
+        <v>975</v>
+      </c>
+      <c r="E2" s="20" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0.06883920677024125</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>0.06194871794871794</v>
+      </c>
+      <c r="I2" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2" s="23" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K2" s="24" t="n">
+        <v>0.2935779816513762</v>
+      </c>
+      <c r="L2" s="25" t="n">
+        <v>0.7064220183486238</v>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>Infineon (€14.7bn global), NXP ($12.3bn global), STMicro ($11.8bn global); combined EU-market share ~30%</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>Intel, TSMC, Samsung, Qualcomm, Broadcom, Texas Instruments supply ~70% of EU chip consumption</t>
+        </is>
+      </c>
+      <c r="O2" s="26" t="inlineStr">
+        <is>
+          <t>SIA/WSTS 2025 actuals; WSTS Autumn 2026 forecast ($975bn); ESIA Europe data ($54.5bn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>SEMICONDUCTORS</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>AI Chips (Logic + AI Memory)</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>280</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>No scaled EU AI chip company; Axelera AI, SiPearl are pre-scale (&lt;$50M combined)</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>NVIDIA ($130bn+ DC rev), AMD ($10bn+), Google/AWS/Meta custom silicon ($15bn+); 100% of EU AI chip supply</t>
+        </is>
+      </c>
+      <c r="O3" s="26" t="inlineStr">
+        <is>
+          <t>Silicon Analysts; Deloitte 2026 Outlook; AI chips ~50% of total semi revenue by value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>SEMICONDUCTORS</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>125</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>ASML (€32.7bn / ~$35.5bn global rev); Zeiss, BESI, ASM Intl (~$2.5bn combined EU rev)</t>
+        </is>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Applied Materials, Lam Research, Tokyo Electron, KLA, Screen (~$2bn EU-origin rev)</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>ASML Annual Report 2025; EU dominates via ASML EUV monopoly; equipment is EU strength area</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr"/>
+      <c r="O4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>SEMICONDUCTORS</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Power / Automotive / Industrial Chips</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>Infineon (~$10bn EU auto/industrial), NXP (~$5bn EU), STMicro (~$4bn EU); ~60% of EU segment</t>
+        </is>
+      </c>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>Texas Instruments, ON Semi, Renesas, Microchip; ~40% of EU power/auto segment</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>Company annual reports; EU has strong position in automotive/power semis</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr"/>
+      <c r="O5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>SEMICONDUCTORS</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>High Bandwidth Memory (HBM)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>No EU HBM producer</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>SK Hynix (~50% global), Samsung (~40%), Micron (~10%); 100% of EU HBM is imported</t>
+        </is>
+      </c>
+      <c r="O6" s="26" t="inlineStr">
+        <is>
+          <t>Deloitte; industry estimates; HBM critical for AI training/inference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CLOUD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Services (IaaS/PaaS/Hosted Private Cloud)</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>350</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>435</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>87</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>108</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>0.2485714285714286</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>0.2482758620689655</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J7" s="23" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="K7" s="24" t="n">
+        <v>0.1505747126436782</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <v>0.8494252873563219</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>OVHcloud (~$1bn), SAP (~$1.7bn cloud infra), Deutsche Telekom/T-Systems (~$1.7bn), Scaleway, STACKIT, others (~$8.7bn)</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>AWS (~30%), Azure (~25%), Google Cloud (~15%); combined ~70% of EU cloud infra = ~$61bn</t>
+        </is>
+      </c>
+      <c r="O7" s="31" t="inlineStr">
+        <is>
+          <t>Synergy Research Group 2025; EU market ~€61bn ($70bn) in 2024, growing 24% YoY; EU providers at 15% share</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CLOUD</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SaaS (Software as a Service)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>430</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>86</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="K8" s="24" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>SAP ($8bn+ EU SaaS), Dassault Systemes, Sage, TeamViewer, others; ~10% of EU SaaS spend</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft 365, Salesforce, Google Workspace, ServiceNow, Oracle; ~90% of EU SaaS spend</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>Grand View Research; Fortune BI; SAP is largest EU SaaS provider; US dominance even more acute than IaaS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CLOUD</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sovereign Cloud Services</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>OVHcloud, T-Systems, STACKIT, Scaleway, S3NS (Thales-Google JV); ~80% of EU sovereign cloud</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>AWS Sovereign Cloud (GA Jan 2026), Azure sovereign controls; ~20% via US sovereign offerings</t>
+        </is>
+      </c>
+      <c r="O9" s="31" t="inlineStr">
+        <is>
+          <t>Broadcom sovereign cloud report; EC €180M tender Apr 2026; EU sovereign cloud projected to reach €100bn by 2031</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AI DATACENTERS</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Data Center Market (Total: colocation, hyperscale, enterprise)</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>270</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>301</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.2507246376811594</v>
+      </c>
+      <c r="L10" s="25" t="n">
+        <v>0.7507246376811594</v>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>Equinix (US-HQ, ~$5bn EU rev), Digital Realty (US-HQ, ~$2bn EU rev), EU telecoms, Interxion; ~25% EU-HQ</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>AWS, Microsoft, Google build ~60% of new EU capacity; US-HQ operators dominate hyperscale segment</t>
+        </is>
+      </c>
+      <c r="O10" s="34" t="inlineStr">
+        <is>
+          <t>Fortune BI; Mordor Intel; EU at ~25.6% of global; hyperscale self-built fastest growing at 19% CAGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>AI DATACENTERS</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Data Center Colocation (EU only)</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.2489626556016597</v>
+      </c>
+      <c r="L11" s="25" t="n">
+        <v>0.7510373443983402</v>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Interxion/Digital Realty (US-HQ), DATA4, AtosOrigin, EU telecoms; ~25% EU-HQ operators</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Equinix (US), Digital Realty (US), CyrusOne (US), NTT (Japan) dominate EU colocation; ~75% non-EU HQ</t>
+        </is>
+      </c>
+      <c r="O11" s="34" t="inlineStr">
+        <is>
+          <t>Research &amp; Markets Q2 2026; growing 17.3% YoY; AI/GPU workloads key driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>AI DATACENTERS</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>AI Accelerator / GPU Market</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>160</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>No EU AI accelerator at scale; Axelera AI (&lt;$50M), SiPearl (&lt;$20M) are early-stage</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>NVIDIA (~80% share = ~$12.8bn EU), AMD (~7%), Google TPU, AWS Trainium, Broadcom ASICs</t>
+        </is>
+      </c>
+      <c r="O12" s="34" t="inlineStr">
+        <is>
+          <t>Silicon Analysts; EU ~10% of global AI accelerator consumption; 100% imported; US export control risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>LLMs</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>LLM Market (Models, APIs, Enterprise SW)</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="38" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="I13" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>Mistral AI ($400M ARR, ~60% from EU = ~$240M EU); Aleph Alpha (~$30M EU); others ~$230M</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI (~29% share), Anthropic (~31% share), Google, Meta, xAI; ~75% of EU LLM spend goes to US providers</t>
+        </is>
+      </c>
+      <c r="O13" s="39" t="inlineStr">
+        <is>
+          <t>AllTechMagazine; Precedence Research; Mistral targeting $1bn rev 2026; EU ~20% of global LLM market</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>LLMs</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Spend (Training + Inference Compute)</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>581.7</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>700</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>58</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>70</v>
+      </c>
+      <c r="G14" s="38" t="n">
+        <v>0.09970775313735601</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>EuroHPC (€7bn budget), Mistral Compute JV, EU national AI compute; ~10% of EU AI infra spend is EU-controlled</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>NVIDIA, US hyperscalers (AWS/Azure/GCP), AMD provide ~90% of EU AI compute infrastructure</t>
+        </is>
+      </c>
+      <c r="O14" s="39" t="inlineStr">
+        <is>
+          <t>Gartner 2026; AllTechMagazine; EU ~10% of global; mostly consumed via US cloud platforms</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>QUANTUM</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Quantum Computing (Hardware, Software, Services)</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G15" s="41" t="n">
+        <v>0.2526315789473684</v>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>IQM ($36M / ~€31M global), Pasqal (€16.5M commercial), AQT, QuiX (~$10M combined); ~42% EU-HQ share of EU market</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>IBM Quantum, Google, Amazon Braket, IonQ ($130M global), Quantinuum, D-Wave; ~58% of EU quantum spend</t>
+        </is>
+      </c>
+      <c r="O15" s="42" t="inlineStr">
+        <is>
+          <t>QED-C 2026 Report; Precedence Research; Europe ~25% of global quantum market; EU companies competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>QUANTUM</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Quantum Sensing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G16" s="41" t="n">
+        <v>0.297872340425532</v>
+      </c>
+      <c r="H16" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="L16" s="25" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>ID Quantique (Swiss), Thales, Airbus Defence, EU quantum startups; ~57% EU-HQ share</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>US defence contractors, Toshiba (Japan) in QKD; ~43% non-EU</t>
+        </is>
+      </c>
+      <c r="O16" s="42" t="inlineStr">
+        <is>
+          <t>QED-C 2026 Report; EU strong in quantum sensing/comms, esp. QKD; grows to $1.1bn globally by 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>QUANTUM</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Cryogenic &amp; Quantum Enabling Equipment</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="40" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G17" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>Bluefors (Finland, global leader in dilution refrigerators ~$100M+), EU cryo/control electronics startups; ~80% EU-HQ</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>US enabling tech companies; ~20% non-EU</t>
+        </is>
+      </c>
+      <c r="O17" s="42" t="inlineStr">
+        <is>
+          <t>Industry estimates; Bluefors is dominant global cryogenics supplier; EU strength area</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>KEY TAKEAWAYS: EU REVENUE CAPTURE ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>EU STRENGTH</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies (led by ASML) capture ~95% of EU equipment revenue (~$36bn of $38bn). ASML's EUV monopoly is the EU's strongest strategic asset in the entire tech stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Power / Auto / Industrial Chips</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>EU STRENGTH</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies (Infineon, NXP, STMicro) capture ~60% of EU segment revenue (~$16.8bn of $28bn). Strong competitive position in mainstream and specialty chips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>Quantum Enabling Equipment</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>EU STRENGTH</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies (Bluefors, startups) capture ~80% of EU segment (~$0.12bn of $0.15bn). Bluefors is the global leader in dilution refrigerators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Sovereign Cloud</t>
+        </is>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>EU MODERATE</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ providers capture ~80% of emerging sovereign cloud segment (~$2.8bn of $3.5bn). Growing fast from small base; EC tender sets precedent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Quantum Computing</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>EU MODERATE</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies (IQM, Pasqal, AQT, QuiX) capture ~42% of EU quantum market (~$0.20bn of $0.48bn). Competitive but US platforms dominate cloud access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure (IaaS/PaaS)</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="inlineStr">
+        <is>
+          <t>EU WEAK</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ providers capture only ~15% of EU cloud infra market (~$13.1bn of $87bn). US hyperscalers invest €10bn/quarter in EU, making gap structurally unbridgeable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>LLMs / AI Models</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>EU WEAK</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>EU companies (led by Mistral) capture ~25% of EU LLM spend (~$0.5bn of $2bn). Mistral growing fast but US models (OpenAI, Anthropic, Google) dominate enterprise use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>AI Accelerators / GPUs</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>EU CRITICAL GAP</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies capture 0% of EU AI accelerator spend (~$0 of $16bn). Total dependency on NVIDIA/AMD. No EU company produces AI GPUs at scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>AI Chips (Logic + Memory)</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>EU CRITICAL GAP</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies capture 0% of EU AI chip consumption (~$0 of $5bn). EU has no leading-edge AI chip design or HBM memory production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>EU CRITICAL GAP</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>EU-controlled compute is only ~10% of EU AI infrastructure spend (~$5.8bn of $58bn). 90% flows through US cloud platforms and US-designed hardware.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O17"/>
+  <mergeCells count="12">
+    <mergeCell ref="C28:O28"/>
+    <mergeCell ref="C27:O27"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="C23:O23"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="C20:O20"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="C29:O29"/>
+    <mergeCell ref="C21:O21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="C25:O25"/>
+    <mergeCell ref="C24:O24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
+++ b/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dependency Analysis'!$A$1:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Market Sizing &amp; EU Revenue'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Market Sizing &amp; EU Revenue'!$A$1:$Q$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -85,7 +85,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -172,6 +172,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E0EC"/>
+        <bgColor rgb="00E6E0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
         <bgColor rgb="001F3864"/>
       </patternFill>
@@ -209,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -286,14 +298,14 @@
     <xf numFmtId="165" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -337,20 +349,20 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3421,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3438,7 +3450,9 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="55" customHeight="1">
@@ -3454,83 +3468,81 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>GLOBAL MARKET SIZE 2025
-(USD bn)</t>
+          <t>GLOBAL MARKET SIZE 2025 (USD bn)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GLOBAL MARKET SIZE 2026E
-(USD bn)</t>
+          <t>GLOBAL MARKET SIZE 2035E (USD bn)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>EU MARKET SIZE 2025
-(USD bn)</t>
+          <t>EU MARKET SIZE 2025 (USD bn)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>EU MARKET SIZE 2026E
-(USD bn)</t>
+          <t>EU MARKET SIZE 2035E (USD bn)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>EU AS % OF
-GLOBAL (2025)</t>
+          <t>EU AS % OF GLOBAL (2025)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>EU AS % OF
-GLOBAL (2026E)</t>
+          <t>EU AS % OF GLOBAL (2035E)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>EU REVENUE CAPTURED BY
-EU-HQ COMPANIES (USD bn, 2025)</t>
+          <t>EU REVENUE CAPTURED BY EU-HQ COMPANIES (USD bn 2025)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EU REVENUE CAPTURED BY
-NON-EU COMPANIES (USD bn, 2025)</t>
+          <t>EU REVENUE CAPTURED BY NON-EU COMPANIES (USD bn 2025)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>% CAPTURED BY
-EU COMPANIES</t>
+          <t>% CAPTURED BY EU COMPANIES</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>% CAPTURED BY
-NON-EU COMPANIES</t>
+          <t>% CAPTURED BY NON-EU COMPANIES</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>KEY EU COMPANIES
-(Revenue, 2025)</t>
+          <t>KEY EU COMPANIES (Revenue 2025)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>KEY NON-EU COMPANIES
-(Share of EU Market)</t>
+          <t>KEY NON-EU COMPANIES (Share of EU Market)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>BASE CASE GROWTH EXPECTATIONS THROUGH 2035</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>WHAT EU NEEDS TO DO FOR SELF-RELIANCE BY 2035</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>SOURCE / NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>SEMICONDUCTORS</t>
@@ -3545,19 +3557,19 @@
         <v>791.7</v>
       </c>
       <c r="D2" s="20" t="n">
-        <v>975</v>
+        <v>1280</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>54.5</v>
       </c>
       <c r="F2" s="20" t="n">
-        <v>60.4</v>
+        <v>130</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>0.06883920677024125</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H2" s="21" t="n">
-        <v>0.06194871794871794</v>
+        <v>0.102</v>
       </c>
       <c r="I2" s="22" t="n">
         <v>16</v>
@@ -3566,14 +3578,14 @@
         <v>38.5</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>0.2935779816513762</v>
+        <v>0.29</v>
       </c>
       <c r="L2" s="25" t="n">
-        <v>0.7064220183486238</v>
+        <v>0.71</v>
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>Infineon (€14.7bn global), NXP ($12.3bn global), STMicro ($11.8bn global); combined EU-market share ~30%</t>
+          <t>Infineon (EUR14.7bn global), NXP ($12.3bn global), STMicro ($11.8bn global); combined EU-market share ~30%</t>
         </is>
       </c>
       <c r="N2" s="15" t="inlineStr">
@@ -3583,11 +3595,21 @@
       </c>
       <c r="O2" s="26" t="inlineStr">
         <is>
-          <t>SIA/WSTS 2025 actuals; WSTS Autumn 2026 forecast ($975bn); ESIA Europe data ($54.5bn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="70" customHeight="1">
+          <t>Global market grows at ~5-7% CAGR to $1.1-1.4T by 2035. AI logic and memory drive &gt;60% of revenue growth. EU share of global production rises from ~10% to 15-20% if Chips Act 2.0 targets are met. Automotive and power electronics remain EU strength segments, growing at 8-9% CAGR.</t>
+        </is>
+      </c>
+      <c r="P2" s="27" t="inlineStr">
+        <is>
+          <t>EU must operationalise the 3nm open foundry by 2033 and ramp to volume by 2035. Must reach 20% global production share (Chips Act target). Requires EUR 120bn mobilisation on schedule, coordinated demand from AI Gigafactories and CADA. Must build integrated design-to-packaging capability rather than isolated fab capacity. Workforce gap of 30-50K must be closed through competence centres and immigration reform.</t>
+        </is>
+      </c>
+      <c r="Q2" s="28" t="inlineStr">
+        <is>
+          <t>SIA/WSTS 2025 actuals; Precedence Research 2035 forecast ($1,277bn); Expert Market Research ($1,413bn); EU share assumes Chips Act 2.0 targets partially met</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>SEMICONDUCTORS</t>
@@ -3602,19 +3624,19 @@
         <v>200</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>280</v>
+        <v>750</v>
       </c>
       <c r="E3" s="20" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="G3" s="21" t="n">
         <v>0.025</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.1</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>0</v>
@@ -3630,7 +3652,7 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>No scaled EU AI chip company; Axelera AI, SiPearl are pre-scale (&lt;$50M combined)</t>
+          <t>No scaled EU AI chip company; Axelera AI and SiPearl are pre-scale (&lt;$50M combined)</t>
         </is>
       </c>
       <c r="N3" s="15" t="inlineStr">
@@ -3640,11 +3662,21 @@
       </c>
       <c r="O3" s="26" t="inlineStr">
         <is>
-          <t>Silicon Analysts; Deloitte 2026 Outlook; AI chips ~50% of total semi revenue by value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
+          <t>AI chips grow at 14-18% CAGR to $600-1,000bn by 2035, becoming ~55-60% of total semiconductor market. Inference chips overtake training chips by revenue (~65% of AI chip spend by 2035). Custom ASICs grow fastest as hyperscalers verticalise. EU consumption grows 10x as AI Gigafactories and data centres scale up.</t>
+        </is>
+      </c>
+      <c r="P3" s="27" t="inlineStr">
+        <is>
+          <t>EU must develop at least 2-3 scaled AI chip design companies (current startups Axelera, SiPearl must reach &gt;$1bn revenue each). Requires Grand Challenges funding, preferential public procurement, and guaranteed manufacturing access at EU foundry. Must build EU-based EDA toolchain or secure long-term strategic partnership with EDA vendors. Target: 15-20% of EU AI chip consumption sourced from EU-designed chips by 2035.</t>
+        </is>
+      </c>
+      <c r="Q3" s="28" t="inlineStr">
+        <is>
+          <t>Research &amp; Markets ($1T AI accelerator chips by 2035); SNS Insider ($746bn); Deloitte 2026 Outlook; inference shift per Silicon Analysts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>SEMICONDUCTORS</t>
@@ -3659,49 +3691,59 @@
         <v>110</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="E4" s="20" t="n">
         <v>38</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="G4" s="21" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="I4" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="J4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="24" t="inlineStr">
-        <is>
-          <t>ASML (€32.7bn / ~$35.5bn global rev); Zeiss, BESI, ASM Intl (~$2.5bn combined EU rev)</t>
-        </is>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L4" s="25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>ASML (EUR32.7bn / ~$35.5bn global rev); Zeiss, BESI, ASM Intl (~$2.5bn combined EU rev)</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>Applied Materials, Lam Research, Tokyo Electron, KLA, Screen (~$2bn EU-origin rev)</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>ASML Annual Report 2025; EU dominates via ASML EUV monopoly; equipment is EU strength area</t>
-        </is>
-      </c>
-      <c r="N4" s="15" t="inlineStr"/>
-      <c r="O4" s="26" t="inlineStr"/>
-    </row>
-    <row r="5" ht="70" customHeight="1">
+      <c r="O4" s="26" t="inlineStr">
+        <is>
+          <t>Equipment market grows at ~7% CAGR to ~$220bn by 2035. EUV and High-NA EUV demand accelerates as sub-3nm nodes proliferate. ASML revenue target $44-60bn by 2030. Advanced packaging equipment segment grows fastest at 12-15% CAGR. EU maintains dominant position through ASML monopoly.</t>
+        </is>
+      </c>
+      <c r="P4" s="27" t="inlineStr">
+        <is>
+          <t>EU must maintain and extend ASML's technological lead (High-NA EUV and beyond). Must develop EU-based capabilities in etch, deposition, and inspection to reduce dependence on Applied Materials/Lam Research/TEL. Should invest in advanced packaging equipment (currently Asia-dominated). Must manage export control alignment with allies carefully to preserve commercial viability while protecting security interests.</t>
+        </is>
+      </c>
+      <c r="Q4" s="28" t="inlineStr">
+        <is>
+          <t>ASML Annual Report 2025 (2030 target $44-60bn); industry growth estimates; EU maintains ~35% global equipment revenue share</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>SEMICONDUCTORS</t>
@@ -3716,49 +3758,59 @@
         <v>95</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="E5" s="20" t="n">
         <v>28</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G5" s="21" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="I5" s="22" t="n">
         <v>16.8</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="J5" s="23" t="n">
         <v>11.2</v>
       </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>Infineon (~$10bn EU auto/industrial), NXP (~$5bn EU), STMicro (~$4bn EU); ~60% of EU segment</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>Texas Instruments, ON Semi, Renesas, Microchip; ~40% of EU power/auto segment</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>Company annual reports; EU has strong position in automotive/power semis</t>
-        </is>
-      </c>
-      <c r="N5" s="15" t="inlineStr"/>
-      <c r="O5" s="26" t="inlineStr"/>
-    </row>
-    <row r="6" ht="70" customHeight="1">
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t>Segment grows at ~7-9% CAGR to ~$200bn by 2035, driven by EV penetration reaching 60-70% of new EU car sales, industrial automation, and energy transition (smart grids, renewables). SiC and GaN wide-bandgap semiconductors grow at 20%+ CAGR. EU strengthens position as global automotive chip leader.</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>EU must defend and extend leadership in automotive/power chips. Requires continued investment in SiC/GaN fab capacity (Infineon, STMicro expanding). Must capture AI-in-vehicle chip opportunity (edge inference for autonomous driving). Should leverage automotive OEM relationships to create demand pull for EU-designed chips. Ensure raw material supply (SiC substrates, gallium) via Critical Raw Materials Act diversification.</t>
+        </is>
+      </c>
+      <c r="Q5" s="28" t="inlineStr">
+        <is>
+          <t>Company annual reports; EU automotive chip share grows as EV adoption accelerates; SiC/GaN CAGR from industry consensus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>SEMICONDUCTORS</t>
@@ -3773,19 +3825,19 @@
         <v>28</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>1.5</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="22" t="n">
         <v>0</v>
@@ -3811,11 +3863,21 @@
       </c>
       <c r="O6" s="26" t="inlineStr">
         <is>
-          <t>Deloitte; industry estimates; HBM critical for AI training/inference</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
+          <t>HBM market grows at ~18-20% CAGR to $120-180bn by 2035 as AI training/inference scales. HBM4 and HBM5 generations increase bandwidth and capacity. Memory becomes bottleneck for AI compute scaling. EU consumption grows 10x with AI Gigafactory buildout but remains 100% import-dependent without intervention.</t>
+        </is>
+      </c>
+      <c r="P6" s="27" t="inlineStr">
+        <is>
+          <t>EU must establish domestic memory R&amp;D and pilot production capability. Could pursue strategic partnership with one major memory manufacturer (SK Hynix, Samsung, or Micron) for EU-based HBM packaging facility. Should fund advanced memory research through Chips for Europe Initiative. Minimum viable goal: EU-based HBM packaging/testing by 2032, capturing 10-15% of EU HBM consumption. Full domestic production is unrealistic by 2035.</t>
+        </is>
+      </c>
+      <c r="Q6" s="28" t="inlineStr">
+        <is>
+          <t>Deloitte; industry estimates; HBM CAGR from memory market analysis; EU consumption scales with AI Gigafactories</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>CLOUD</t>
@@ -3830,19 +3892,19 @@
         <v>350</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>435</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>87</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>0.2485714285714286</v>
+        <v>0.249</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>0.2482758620689655</v>
+        <v>0.25</v>
       </c>
       <c r="I7" s="22" t="n">
         <v>13.1</v>
@@ -3851,10 +3913,10 @@
         <v>73.90000000000001</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>0.1505747126436782</v>
+        <v>0.15</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>0.8494252873563219</v>
+        <v>0.85</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -3866,13 +3928,23 @@
           <t>AWS (~30%), Azure (~25%), Google Cloud (~15%); combined ~70% of EU cloud infra = ~$61bn</t>
         </is>
       </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t>Synergy Research Group 2025; EU market ~€61bn ($70bn) in 2024, growing 24% YoY; EU providers at 15% share</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
+      <c r="O7" s="26" t="inlineStr">
+        <is>
+          <t>Cloud infra grows at ~13-15% CAGR to $1,000-1,400bn by 2035. AI workloads drive majority of incremental growth. EU market grows ~3.4x from $87bn to ~$300bn. EU provider market share unlikely to exceed 20% without massive intervention; US hyperscalers continue investing EUR 10bn/quarter in EU. Sovereign cloud segment grows fastest at 25-30% CAGR.</t>
+        </is>
+      </c>
+      <c r="P7" s="27" t="inlineStr">
+        <is>
+          <t>EU must implement CADA sovereignty framework (SEAL levels) and enforce mandatory risk assessments for public-sector cloud procurement. Must triple data centre capacity as planned. Should create interoperable EU cloud standards (GAIA-X evolution). Target: EU providers capture 25-30% of EU cloud market by 2035 (up from 15%). Sovereign cloud must reach EUR 100bn+ and become default for public sector. Open-source-first principle critical for reducing vendor lock-in.</t>
+        </is>
+      </c>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>Future Market Insights ($2,649bn global by 2035); Expert Market Research ($2,478bn); Synergy Research EU share data; CADA tripling target</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CLOUD</t>
@@ -3887,13 +3959,13 @@
         <v>430</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="E8" s="29" t="n">
         <v>86</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>0.2</v>
@@ -3908,7 +3980,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L8" s="25" t="n">
         <v>0.9</v>
@@ -3923,13 +3995,23 @@
           <t>Microsoft 365, Salesforce, Google Workspace, ServiceNow, Oracle; ~90% of EU SaaS spend</t>
         </is>
       </c>
-      <c r="O8" s="31" t="inlineStr">
-        <is>
-          <t>Grand View Research; Fortune BI; SAP is largest EU SaaS provider; US dominance even more acute than IaaS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t>SaaS grows at ~15-16% CAGR to $1,500-2,000bn by 2035. AI-native SaaS (embedded LLMs, copilots) becomes dominant delivery model. EU market grows ~4x to ~$360bn. EU provider share remains under pressure at ~10% without structural change. Enterprise switching costs and ecosystem lock-in favour incumbents.</t>
+        </is>
+      </c>
+      <c r="P8" s="27" t="inlineStr">
+        <is>
+          <t>EU must invest in open-source AI-powered SaaS alternatives for critical government and enterprise functions. Should leverage EU Open Source Strategy and open-source-first procurement principle. SAP must maintain/grow EU market leadership in ERP. EU should nurture next-generation AI-native SaaS startups through public procurement and Chips Fund-type venture support. Target: 15-20% EU provider share by 2035. Self-reliance in SaaS is the hardest segment to achieve.</t>
+        </is>
+      </c>
+      <c r="Q8" s="31" t="inlineStr">
+        <is>
+          <t>ResearchAndMarkets ($3.5T total cloud by 2035); SaaS ~50% of total cloud; EU share remains structurally challenged</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CLOUD</t>
@@ -3944,13 +4026,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>3.5</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>5.6</v>
+        <v>70</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>0.7</v>
@@ -3965,7 +4047,7 @@
         <v>0.7</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L9" s="25" t="n">
         <v>0.2</v>
@@ -3980,13 +4062,23 @@
           <t>AWS Sovereign Cloud (GA Jan 2026), Azure sovereign controls; ~20% via US sovereign offerings</t>
         </is>
       </c>
-      <c r="O9" s="31" t="inlineStr">
-        <is>
-          <t>Broadcom sovereign cloud report; EC €180M tender Apr 2026; EU sovereign cloud projected to reach €100bn by 2031</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
+      <c r="O9" s="26" t="inlineStr">
+        <is>
+          <t>Sovereign cloud grows at ~35% CAGR from small base to $80-120bn globally by 2035. EU is largest sovereign cloud market (70% of global). EU sovereign cloud projected to reach EUR 100bn by 2031, and continue growing. CIO demand strong: 60% of Western European CIOs want more local cloud providers. SEAL framework drives government adoption.</t>
+        </is>
+      </c>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>EU must fully implement CADA SEAL framework and make SEAL-3/SEAL-4 mandatory for sensitive public-sector workloads by 2028. Must ensure 4+ competitive EU sovereign cloud providers scale to EUR 10bn+ revenue each. Should standardise sovereign cloud APIs for portability. Must resolve S3NS-type hybrid arrangements (Thales-Google JV) - determine if these truly count as sovereign. Target: EU-controlled sovereign cloud captures 85%+ of EU public-sector cloud spend by 2035.</t>
+        </is>
+      </c>
+      <c r="Q9" s="31" t="inlineStr">
+        <is>
+          <t>Broadcom sovereign cloud report; Precedence Research sovereign AI infra ($177bn by 2035); EC EUR180M tender precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>AI DATACENTERS</t>
@@ -4001,19 +4093,19 @@
         <v>270</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>301</v>
+        <v>900</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>69</v>
       </c>
       <c r="F10" s="32" t="n">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>0.2555555555555555</v>
+        <v>0.256</v>
       </c>
       <c r="H10" s="33" t="n">
-        <v>0.2558139534883721</v>
+        <v>0.256</v>
       </c>
       <c r="I10" s="22" t="n">
         <v>17.3</v>
@@ -4022,10 +4114,10 @@
         <v>51.8</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.2507246376811594</v>
+        <v>0.25</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>0.7507246376811594</v>
+        <v>0.75</v>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
@@ -4037,13 +4129,23 @@
           <t>AWS, Microsoft, Google build ~60% of new EU capacity; US-HQ operators dominate hyperscale segment</t>
         </is>
       </c>
-      <c r="O10" s="34" t="inlineStr">
-        <is>
-          <t>Fortune BI; Mordor Intel; EU at ~25.6% of global; hyperscale self-built fastest growing at 19% CAGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t>Global DC market grows at ~11-13% CAGR to $700-1,000bn by 2035. AI-dedicated capacity grows at 25%+ CAGR. EU data centre capacity triples per CADA target (from 3.6 GW to ~11 GW by 2033). Energy becomes binding constraint: grid capacity, renewable supply, and cooling technology are key bottlenecks. Secondary EU markets (Spain, Poland, Nordics) grow fastest.</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>EU must deliver CADA tripling target and resolve energy bottleneck through Strategic Roadmap for Digitalisation and AI in Energy. Must streamline permitting (12-month max under Chips Act 2.0 model). Should incentivise EU-HQ data centre operators to scale up. Must ensure new capacity uses EU-designed chips when available (linking CADA to Chips Act 2.0 demand side). Target: EU-HQ operators capture 35-40% of EU DC market by 2035 (up from 25%).</t>
+        </is>
+      </c>
+      <c r="Q10" s="34" t="inlineStr">
+        <is>
+          <t>Spherical Insights ($988bn by 2035); SNS Insider ($882bn); Fortune BI; CADA tripling target; EU energy constraint analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>AI DATACENTERS</t>
@@ -4068,7 +4170,7 @@
         <v>24.1</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>28.3</v>
+        <v>106</v>
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
@@ -4087,10 +4189,10 @@
         <v>18.1</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.2489626556016597</v>
+        <v>0.25</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>0.7510373443983402</v>
+        <v>0.75</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -4102,13 +4204,23 @@
           <t>Equinix (US), Digital Realty (US), CyrusOne (US), NTT (Japan) dominate EU colocation; ~75% non-EU HQ</t>
         </is>
       </c>
-      <c r="O11" s="34" t="inlineStr">
-        <is>
-          <t>Research &amp; Markets Q2 2026; growing 17.3% YoY; AI/GPU workloads key driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="70" customHeight="1">
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t>EU colocation grows at ~12-15% CAGR to ~$100-110bn by 2035. AI and GPU workloads become &gt;40% of colocation revenue. Wholesale colocation grows faster than retail as hyperscalers lease rather than build. Power density requirements increase from 10-15 kW/rack to 50-100+ kW/rack for AI. Liquid cooling becomes standard.</t>
+        </is>
+      </c>
+      <c r="P11" s="27" t="inlineStr">
+        <is>
+          <t>EU must develop EU-headquartered colocation champions through public procurement preferences and strategic project designation. Should require EU data sovereignty compliance for colocation hosting government/critical infrastructure workloads. Must invest in liquid cooling and high-density infrastructure R&amp;D. Target: EU-HQ colocation operators capture 35% of EU market by 2035 (up from 25%).</t>
+        </is>
+      </c>
+      <c r="Q11" s="34" t="inlineStr">
+        <is>
+          <t>NextMSC ($106bn EU colocation by 2035); Research &amp; Markets; AI workload shift drives density and revenue growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>AI DATACENTERS</t>
@@ -4123,19 +4235,19 @@
         <v>160</v>
       </c>
       <c r="D12" s="32" t="n">
-        <v>200</v>
+        <v>750</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>16</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G12" s="33" t="n">
         <v>0.1</v>
       </c>
       <c r="H12" s="33" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I12" s="22" t="n">
         <v>0</v>
@@ -4151,7 +4263,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>No EU AI accelerator at scale; Axelera AI (&lt;$50M), SiPearl (&lt;$20M) are early-stage</t>
+          <t>No EU AI accelerator at scale; Axelera AI (&lt;$50M) and SiPearl (&lt;$20M) are early-stage</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
@@ -4159,13 +4271,23 @@
           <t>NVIDIA (~80% share = ~$12.8bn EU), AMD (~7%), Google TPU, AWS Trainium, Broadcom ASICs</t>
         </is>
       </c>
-      <c r="O12" s="34" t="inlineStr">
-        <is>
-          <t>Silicon Analysts; EU ~10% of global AI accelerator consumption; 100% imported; US export control risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
+      <c r="O12" s="26" t="inlineStr">
+        <is>
+          <t>AI accelerator market grows at ~17-25% CAGR to $430-1,000bn by 2035. Inference overtakes training as primary spend driver (~65% by 2035). Custom ASICs grow fastest at 30%+ CAGR. NVIDIA share gradually erodes from ~80% to ~55-65% as competition broadens. EU consumption grows 5-6x with AI Gigafactory and data centre expansion.</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="inlineStr">
+        <is>
+          <t>EU must bring at least 2 EU-designed AI accelerators to volume production by 2032 (Axelera for inference, SiPearl for HPC, or new entrants). Requires preferential public procurement mandating EU silicon in sovereign AI infrastructure. EU foundry must support AI chip manufacturing. Should create RISC-V based open architecture for inference accelerators to avoid CUDA lock-in. Target: EU-designed accelerators capture 10-15% of EU consumption by 2035. Full self-reliance is not achievable; diversified sourcing is realistic goal.</t>
+        </is>
+      </c>
+      <c r="Q12" s="34" t="inlineStr">
+        <is>
+          <t>Research &amp; Markets ($1T by 2035); Kaiso Research ($432bn); SNS Insider ($746bn); inference shift analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>LLMs</t>
@@ -4180,19 +4302,19 @@
         <v>10</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="E13" s="37" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>2.5</v>
+        <v>35</v>
       </c>
       <c r="G13" s="38" t="n">
         <v>0.2</v>
       </c>
       <c r="H13" s="38" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="I13" s="22" t="n">
         <v>0.5</v>
@@ -4216,13 +4338,23 @@
           <t>OpenAI (~29% share), Anthropic (~31% share), Google, Meta, xAI; ~75% of EU LLM spend goes to US providers</t>
         </is>
       </c>
-      <c r="O13" s="39" t="inlineStr">
-        <is>
-          <t>AllTechMagazine; Precedence Research; Mistral targeting $1bn rev 2026; EU ~20% of global LLM market</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="70" customHeight="1">
+      <c r="O13" s="26" t="inlineStr">
+        <is>
+          <t>LLM market grows at ~34% CAGR to $150bn by 2035. Market shifts from general-purpose to domain-specific fine-tuned models. Open-weight models gain share vs. proprietary APIs. Inference costs decline 10x, democratising deployment. EU LLM market grows to ~$35bn as enterprise adoption reaches 80%+ penetration. Mistral targets $5-10bn revenue by 2030.</t>
+        </is>
+      </c>
+      <c r="P13" s="27" t="inlineStr">
+        <is>
+          <t>EU must ensure Mistral and other EU model developers reach frontier capability parity. Requires AI Gigafactory compute access for training next-generation models. Must implement open-source-first principle for public-sector AI procurement (CADA). Should fund multilingual EU-specific model development for all 24 official languages. Must build EU model evaluation and safety framework. Target: EU-developed models serve 35-40% of EU LLM market by 2035 (up from 25%).</t>
+        </is>
+      </c>
+      <c r="Q13" s="39" t="inlineStr">
+        <is>
+          <t>Precedence Research ($150bn by 2035); Roots Analysis ($180bn); Mistral revenue trajectory; enterprise AI adoption curves</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>LLMs</t>
@@ -4237,19 +4369,19 @@
         <v>581.7</v>
       </c>
       <c r="D14" s="37" t="n">
-        <v>700</v>
+        <v>2500</v>
       </c>
       <c r="E14" s="37" t="n">
         <v>58</v>
       </c>
       <c r="F14" s="37" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.09970775313735601</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I14" s="22" t="n">
         <v>5.8</v>
@@ -4258,14 +4390,14 @@
         <v>52.2</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L14" s="25" t="n">
         <v>0.9</v>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>EuroHPC (€7bn budget), Mistral Compute JV, EU national AI compute; ~10% of EU AI infra spend is EU-controlled</t>
+          <t>EuroHPC (EUR7bn budget), Mistral Compute JV, EU national AI compute; ~10% of EU AI infra spend is EU-controlled</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -4273,13 +4405,23 @@
           <t>NVIDIA, US hyperscalers (AWS/Azure/GCP), AMD provide ~90% of EU AI compute infrastructure</t>
         </is>
       </c>
-      <c r="O14" s="39" t="inlineStr">
-        <is>
-          <t>Gartner 2026; AllTechMagazine; EU ~10% of global; mostly consumed via US cloud platforms</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="70" customHeight="1">
+      <c r="O14" s="26" t="inlineStr">
+        <is>
+          <t>Global AI infrastructure spending grows at ~16% CAGR to $2,000-3,000bn by 2035. Inference infrastructure overtakes training by 2028-2030. Edge AI inference grows at 25%+ CAGR. EU AI infra spend grows 5x to ~$300bn. Currently 90% flows through US platforms; CADA and Chips Act 2.0 aim to redirect significant portion toward EU-controlled infrastructure.</t>
+        </is>
+      </c>
+      <c r="P14" s="27" t="inlineStr">
+        <is>
+          <t>EU must operationalise AI Gigafactories (75,000+ accelerators each) by 2028-2030 as planned. Must build sovereign AI compute layer using EU-designed chips when available. Requires EuroHPC expansion and new Mistral Compute-type JVs. Must train EU workforce in AI infrastructure operations. Should mandate that public-funded AI research uses EU-hosted compute. Target: 25-30% of EU AI infrastructure spend flows through EU-controlled platforms by 2035 (up from 10%).</t>
+        </is>
+      </c>
+      <c r="Q14" s="39" t="inlineStr">
+        <is>
+          <t>Gartner ($2.52T total AI spending in 2026); projected CAGR through 2035; CADA and AI Gigafactory programme targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>QUANTUM</t>
@@ -4294,19 +4436,19 @@
         <v>1.9</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E15" s="40" t="n">
         <v>0.48</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>0.63</v>
+        <v>5</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>0.2526315789473684</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="41" t="n">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="22" t="n">
         <v>0.2</v>
@@ -4315,14 +4457,14 @@
         <v>0.28</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.42</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.58</v>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>IQM ($36M / ~€31M global), Pasqal (€16.5M commercial), AQT, QuiX (~$10M combined); ~42% EU-HQ share of EU market</t>
+          <t>IQM ($36M / ~EUR31M global), Pasqal (EUR16.5M commercial), AQT, QuiX (~$10M combined); ~42% EU-HQ share of EU market</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
@@ -4330,13 +4472,23 @@
           <t>IBM Quantum, Google, Amazon Braket, IonQ ($130M global), Quantinuum, D-Wave; ~58% of EU quantum spend</t>
         </is>
       </c>
-      <c r="O15" s="42" t="inlineStr">
-        <is>
-          <t>QED-C 2026 Report; Precedence Research; Europe ~25% of global quantum market; EU companies competitive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="70" customHeight="1">
+      <c r="O15" s="26" t="inlineStr">
+        <is>
+          <t>Quantum computing grows at ~27-35% CAGR to $19-46bn by 2035. Fault-tolerant quantum computing expected to emerge by early 2030s. Quantum-as-a-Service becomes dominant delivery model. Pharma, finance, logistics and materials science are first commercial verticals. EU maintains ~25% of global market with strong hardware diversity.</t>
+        </is>
+      </c>
+      <c r="P15" s="27" t="inlineStr">
+        <is>
+          <t>EU must scale IQM, Pasqal, AQT, and QuiX from pilot-line prototypes to commercial-grade production by 2030. Requires Quantum Act coordination with Chips Act 2.0 (shared foundry infrastructure). Must build EU quantum cloud platform to counter IBM/Amazon/Google/Azure dominance. Should industrialise all 6 quantum pilot lines and select 2-3 for commercial fab. Target: EU-HQ companies capture 50%+ of EU quantum market by 2035 (up from 42%).</t>
+        </is>
+      </c>
+      <c r="Q15" s="42" t="inlineStr">
+        <is>
+          <t>Precedence Research ($19.4bn by 2035); Vantage ($45.6bn); SNS Insider ($18.9bn); QED-C 2026 Report; Europe ~25% share maintained</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>QUANTUM</t>
@@ -4351,16 +4503,16 @@
         <v>0.47</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="40" t="n">
         <v>0.14</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>0.18</v>
+        <v>0.9</v>
       </c>
       <c r="G16" s="41" t="n">
-        <v>0.297872340425532</v>
+        <v>0.3</v>
       </c>
       <c r="H16" s="41" t="n">
         <v>0.3</v>
@@ -4372,10 +4524,10 @@
         <v>0.06</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.57</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.43</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -4387,13 +4539,23 @@
           <t>US defence contractors, Toshiba (Japan) in QKD; ~43% non-EU</t>
         </is>
       </c>
-      <c r="O16" s="42" t="inlineStr">
-        <is>
-          <t>QED-C 2026 Report; EU strong in quantum sensing/comms, esp. QKD; grows to $1.1bn globally by 2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1">
+      <c r="O16" s="26" t="inlineStr">
+        <is>
+          <t>Quantum sensing grows at ~20% CAGR to $2-4bn by 2035. QKD networks expand as PQC threat drives adoption. Quantum sensors deployed in healthcare (MRI), defence (submarine detection), and infrastructure monitoring. EU has strong academic and industrial base, especially in QKD and atomic sensors.</t>
+        </is>
+      </c>
+      <c r="P16" s="27" t="inlineStr">
+        <is>
+          <t>EU must commercialise QKD technology for critical infrastructure (telecoms, finance, government). Should build pan-EU quantum-secured communication network by 2035 (EuroQCI initiative). Must support quantum sensor startups in navigating defence procurement. Leverage EU strength in photonics (PIXEurope) for integrated quantum sensing chips. Target: EU-HQ companies capture 65%+ of EU quantum sensing/comms market by 2035 (up from 57%).</t>
+        </is>
+      </c>
+      <c r="Q16" s="42" t="inlineStr">
+        <is>
+          <t>QED-C 2026 Report (sensing grows to $1.1bn by 2028); projected 2035 based on continued 18-20% CAGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>QUANTUM</t>
@@ -4408,13 +4570,13 @@
         <v>0.3</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0.38</v>
+        <v>1.5</v>
       </c>
       <c r="E17" s="40" t="n">
         <v>0.15</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
       <c r="G17" s="41" t="n">
         <v>0.5</v>
@@ -4444,207 +4606,213 @@
           <t>US enabling tech companies; ~20% non-EU</t>
         </is>
       </c>
-      <c r="O17" s="42" t="inlineStr">
-        <is>
-          <t>Industry estimates; Bluefors is dominant global cryogenics supplier; EU strength area</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+      <c r="O17" s="26" t="inlineStr">
+        <is>
+          <t>Cryogenic and enabling equipment grows at ~17% CAGR to $1-2bn by 2035 as quantum computing scales. Dilution refrigerator demand grows with every new quantum system deployment. Control electronics and interconnect markets emerge as quantum processors scale beyond 1000 qubits. EU maintains strong position through Bluefors dominance.</t>
+        </is>
+      </c>
+      <c r="P17" s="27" t="inlineStr">
+        <is>
+          <t>EU must maintain Bluefors leadership and expand into adjacent enabling technologies (cryogenic CMOS, photonic interconnects, modular packaging). Chips JU quantum-enabling calls must fund industrialisation not just R&amp;D. Should create EU supply chain for helium-3 (critical for cryogenics). Must develop EU-based quantum control electronics stack. Target: EU-HQ companies maintain 80%+ of EU enabling equipment market and capture 60%+ of global market.</t>
+        </is>
+      </c>
+      <c r="Q17" s="42" t="inlineStr">
+        <is>
+          <t>Industry estimates; Bluefors dominance; Chips JU EUR 20m quantum-enabling call; market scales with quantum system deployments</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>KEY TAKEAWAYS: EU SELF-RELIANCE ROADMAP TO 2035</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>KEY TAKEAWAYS: EU REVENUE CAPTURE ANALYSIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="35" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
           <t>Semiconductor Equipment</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>EU STRENGTH</t>
         </is>
       </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>EU-HQ companies capture ~95% of EU equipment revenue. ASML's High-NA EUV ensures continued dominance through 2035. Maintain lead and expand into adjacent equipment categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>Power / Auto / Industrial Chips</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>EU STRENGTH</t>
+        </is>
+      </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies (led by ASML) capture ~95% of EU equipment revenue (~$36bn of $38bn). ASML's EUV monopoly is the EU's strongest strategic asset in the entire tech stack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="35" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
-        <is>
-          <t>Power / Auto / Industrial Chips</t>
-        </is>
-      </c>
-      <c r="B21" s="46" t="inlineStr">
+          <t>EU-HQ companies capture ~60%. EU automotive chip leadership grows with EV transition. SiC/GaN investment and edge AI for vehicles are key growth vectors to reach 65%+ by 2035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>Quantum Enabling Equipment</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>EU STRENGTH</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies (Infineon, NXP, STMicro) capture ~60% of EU segment revenue (~$16.8bn of $28bn). Strong competitive position in mainstream and specialty chips.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="35" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
-        <is>
-          <t>Quantum Enabling Equipment</t>
+          <t>EU-HQ companies capture ~80%. Bluefors dominance in cryogenics is a global asset. Must industrialise control electronics and interconnects as quantum scales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Sovereign Cloud</t>
         </is>
       </c>
       <c r="B22" s="46" t="inlineStr">
         <is>
-          <t>EU STRENGTH</t>
+          <t>EU ON TRACK</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies (Bluefors, startups) capture ~80% of EU segment (~$0.12bn of $0.15bn). Bluefors is the global leader in dilution refrigerators.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="35" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t>Sovereign Cloud</t>
+          <t>EU-HQ capture ~80% of $3.5bn market. Segment grows to ~$70bn EU by 2035. CADA SEAL framework is critical policy lever. Must mandate SEAL-3/4 for public sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
         <is>
-          <t>EU MODERATE</t>
+          <t>EU COMPETITIVE</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ providers capture ~80% of emerging sovereign cloud segment (~$2.8bn of $3.5bn). Growing fast from small base; EC tender sets precedent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="35" customHeight="1">
-      <c r="A24" s="48" t="inlineStr">
-        <is>
-          <t>Quantum Computing</t>
-        </is>
-      </c>
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>EU MODERATE</t>
+          <t>EU-HQ capture ~42% of EU market. Must scale IQM/Pasqal to commercial production and build EU quantum cloud. Target: 50%+ by 2035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>EU CHALLENGED</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies (IQM, Pasqal, AQT, QuiX) capture ~42% of EU quantum market (~$0.20bn of $0.48bn). Competitive but US platforms dominate cloud access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="49" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure (IaaS/PaaS)</t>
-        </is>
-      </c>
-      <c r="B25" s="50" t="inlineStr">
-        <is>
-          <t>EU WEAK</t>
+          <t>EU-HQ capture only 15% of $87bn EU market. Hyperscaler investment gap is structurally unbridgeable. Sovereign cloud is the realistic path; target 25-30% by 2035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>LLMs / AI Models</t>
+        </is>
+      </c>
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>EU GROWING</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ providers capture only ~15% of EU cloud infra market (~$13.1bn of $87bn). US hyperscalers invest €10bn/quarter in EU, making gap structurally unbridgeable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="49" t="inlineStr">
-        <is>
-          <t>LLMs / AI Models</t>
-        </is>
-      </c>
-      <c r="B26" s="50" t="inlineStr">
-        <is>
-          <t>EU WEAK</t>
+          <t>EU capture ~25% (led by Mistral). Must reach frontier model parity and leverage open-source-first procurement. Target: 35-40% by 2035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>AI Accelerators / GPUs</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>EU CRITICAL GAP</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>EU companies (led by Mistral) capture ~25% of EU LLM spend (~$0.5bn of $2bn). Mistral growing fast but US models (OpenAI, Anthropic, Google) dominate enterprise use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="35" customHeight="1">
-      <c r="A27" s="49" t="inlineStr">
-        <is>
-          <t>AI Accelerators / GPUs</t>
-        </is>
-      </c>
-      <c r="B27" s="51" t="inlineStr">
+          <t>EU capture 0% of $16bn EU market. Must bring 2+ EU-designed accelerators to volume by 2032. Target: 10-15% by 2035. Full self-reliance impossible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>AI Chips (Logic + Memory)</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>EU CRITICAL GAP</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies capture 0% of EU AI accelerator spend (~$0 of $16bn). Total dependency on NVIDIA/AMD. No EU company produces AI GPUs at scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="49" t="inlineStr">
-        <is>
-          <t>AI Chips (Logic + Memory)</t>
-        </is>
-      </c>
-      <c r="B28" s="51" t="inlineStr">
+          <t>EU capture 0% of $5bn EU market. Foundry (pilot 2030-33) and Grand Challenges are essential. Target: 15-20% of EU consumption by 2035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>EU CRITICAL GAP</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>EU-HQ companies capture 0% of EU AI chip consumption (~$0 of $5bn). EU has no leading-edge AI chip design or HBM memory production.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="49" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="B29" s="51" t="inlineStr">
-        <is>
-          <t>EU CRITICAL GAP</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>EU-controlled compute is only ~10% of EU AI infrastructure spend (~$5.8bn of $58bn). 90% flows through US cloud platforms and US-designed hardware.</t>
+          <t>EU-controlled is only 10% of $58bn. AI Gigafactories and sovereign compute layer are the path forward. Target: 25-30% by 2035.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
-  <mergeCells count="12">
-    <mergeCell ref="C28:O28"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="C23:O23"/>
-    <mergeCell ref="A19:O19"/>
-    <mergeCell ref="C20:O20"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="C29:O29"/>
-    <mergeCell ref="C21:O21"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="C25:O25"/>
-    <mergeCell ref="C24:O24"/>
+  <autoFilter ref="A1:Q17"/>
+  <mergeCells count="11">
+    <mergeCell ref="C21:Q21"/>
+    <mergeCell ref="C20:Q20"/>
+    <mergeCell ref="A18:Q18"/>
+    <mergeCell ref="C25:Q25"/>
+    <mergeCell ref="C24:Q24"/>
+    <mergeCell ref="C28:Q28"/>
+    <mergeCell ref="C27:Q27"/>
+    <mergeCell ref="C19:Q19"/>
+    <mergeCell ref="C23:Q23"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="C26:Q26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
+++ b/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
@@ -10,10 +10,12 @@
     <sheet name="Dependency Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Market Sizing &amp; EU Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AI Gigafactory &amp; LLM Impact" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dependency Analysis'!$A$1:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Market Sizing &amp; EU Revenue'!$A$1:$Q$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI Gigafactory &amp; LLM Impact'!$A$1:$F$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,7 +83,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="002F5496"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -190,8 +198,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF6600"/>
-        <bgColor rgb="00FF6600"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -352,21 +360,59 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3433,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4622,197 +4668,1564 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>KEY TAKEAWAYS: EU SELF-RELIANCE ROADMAP TO 2035</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>Semiconductor Equipment</t>
-        </is>
-      </c>
-      <c r="B19" s="45" t="inlineStr">
-        <is>
-          <t>EU STRENGTH</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ companies capture ~95% of EU equipment revenue. ASML's High-NA EUV ensures continued dominance through 2035. Maintain lead and expand into adjacent equipment categories.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>Power / Auto / Industrial Chips</t>
-        </is>
-      </c>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>EU STRENGTH</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ companies capture ~60%. EU automotive chip leadership grows with EV transition. SiC/GaN investment and edge AI for vehicles are key growth vectors to reach 65%+ by 2035.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>Quantum Enabling Equipment</t>
-        </is>
-      </c>
-      <c r="B21" s="45" t="inlineStr">
-        <is>
-          <t>EU STRENGTH</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ companies capture ~80%. Bluefors dominance in cryogenics is a global asset. Must industrialise control electronics and interconnects as quantum scales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>Sovereign Cloud</t>
-        </is>
-      </c>
-      <c r="B22" s="46" t="inlineStr">
-        <is>
-          <t>EU ON TRACK</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ capture ~80% of $3.5bn market. Segment grows to ~$70bn EU by 2035. CADA SEAL framework is critical policy lever. Must mandate SEAL-3/4 for public sector.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>Quantum Computing</t>
-        </is>
-      </c>
-      <c r="B23" s="47" t="inlineStr">
-        <is>
-          <t>EU COMPETITIVE</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ capture ~42% of EU market. Must scale IQM/Pasqal to commercial production and build EU quantum cloud. Target: 50%+ by 2035.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>EU CHALLENGED</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>EU-HQ capture only 15% of $87bn EU market. Hyperscaler investment gap is structurally unbridgeable. Sovereign cloud is the realistic path; target 25-30% by 2035.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>LLMs / AI Models</t>
-        </is>
-      </c>
-      <c r="B25" s="47" t="inlineStr">
-        <is>
-          <t>EU GROWING</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>EU capture ~25% (led by Mistral). Must reach frontier model parity and leverage open-source-first procurement. Target: 35-40% by 2035.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>AI Accelerators / GPUs</t>
-        </is>
-      </c>
-      <c r="B26" s="49" t="inlineStr">
-        <is>
-          <t>EU CRITICAL GAP</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>EU capture 0% of $16bn EU market. Must bring 2+ EU-designed accelerators to volume by 2032. Target: 10-15% by 2035. Full self-reliance impossible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>AI Chips (Logic + Memory)</t>
-        </is>
-      </c>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>EU CRITICAL GAP</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>EU capture 0% of $5bn EU market. Foundry (pilot 2030-33) and Grand Challenges are essential. Target: 15-20% of EU consumption by 2035.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="B28" s="49" t="inlineStr">
-        <is>
-          <t>EU CRITICAL GAP</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>EU-controlled is only 10% of $58bn. AI Gigafactories and sovereign compute layer are the path forward. Target: 25-30% by 2035.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:Q17"/>
-  <mergeCells count="11">
-    <mergeCell ref="C21:Q21"/>
-    <mergeCell ref="C20:Q20"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="C25:Q25"/>
-    <mergeCell ref="C24:Q24"/>
-    <mergeCell ref="C28:Q28"/>
-    <mergeCell ref="C27:Q27"/>
-    <mergeCell ref="C19:Q19"/>
-    <mergeCell ref="C23:Q23"/>
-    <mergeCell ref="C22:Q22"/>
-    <mergeCell ref="C26:Q26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECTION</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DETAIL</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VALUE / METRIC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TIMELINE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IMPLICATION FOR EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Initiative Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>InvestAI Facility - AI Gigafactories (AIGF)</t>
+        </is>
+      </c>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>EUR 20bn total public-private partnership, the world's largest for AI</t>
+        </is>
+      </c>
+      <c r="E3" s="45" t="inlineStr">
+        <is>
+          <t>Announced Feb 2025; formal call Summer 2026</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Provides sovereign compute backbone for EU frontier model training and inference</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Managing Entity</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>European High-Performance Computing Joint Undertaking (EuroHPC JU)</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>76 expressions of interest from 16 Member States across 60 sites</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="inlineStr">
+        <is>
+          <t>EuroHPC JU regulation amended Jan 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Centralised coordination ensures pan-EU access; avoids fragmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Number of Facilities</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>7-8 AI Gigafactories expected (up from original 4-5 target)</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>75,000+ advanced AI chips per facility (downscaled from original 100,000+)</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>Construction Phase 1: 2028; Phase 2: 2030</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>More facilities means broader geographic access but potentially less concentrated compute per site</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Total Compute Target</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>525,000-600,000+ advanced AI accelerators across all Gigafactories</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Equivalent to ~4-5x current total EuroHPC AI compute capacity</t>
+        </is>
+      </c>
+      <c r="E6" s="45" t="inlineStr">
+        <is>
+          <t>Fully operational 2030-2032</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>If fully deployed, EU sovereign compute rivals a single major US hyperscaler's 2025 capacity - but US will have grown 5-10x by then</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EU Contribution Cap</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>17% of capital expenditure (CAPEX) per facility, or equivalent in guaranteed compute off-take</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>Member States must at least match EU contribution (17%+); remainder (~66%) from private sector</t>
+        </is>
+      </c>
+      <c r="E7" s="45" t="inlineStr">
+        <is>
+          <t>Per EuroHPC JU regulation (Jan 2026 amendment)</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>34% public funding de-risks private investment but still requires massive private capital mobilisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMME OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Eligible CAPEX</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>GPUs, CPUs, memory, storage, high-performance networking, racks, cooling, rack power, software</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>Does NOT cover physical building or general site utilities</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Focused on compute infrastructure rather than real estate reduces cost but still requires data centre shells</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>EU Budget Contribution (17% CAPEX)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>~EUR 3.4bn (17% of EUR 20bn envelope)</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>EUR 3.4bn</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>2026-2032</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>EU co-financing leverages 5:1 private money; EIB provides additional financing instruments</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Member State Matching (17%+)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>~EUR 3.4-4bn from national budgets (RRF funds, Cohesion Funds, national budgets)</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>EUR 3.4-4bn</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>2026-2032</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Member States can use Recovery and Resilience Facility and Cohesion Fund money</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Private Sector Investment (~66%)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>~EUR 13-14bn from consortia, banks, infrastructure funds</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>EUR 13-14bn</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>2026-2035</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Ardian's AION bid alone is EUR 10bn; signals strong private appetite</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Total InvestAI Envelope</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>EUR 20bn mobilised for AI Gigafactories</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>EUR 20bn</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="inlineStr">
+        <is>
+          <t>2025-2032</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>World's largest public-private AI infrastructure partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Existing AI Factories (2021-2027)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>EUR 10bn total invested in EuroHPC supercomputers + 19 AI Factories</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>13 facilities selected; 9 new AI-optimised supercomputers; ~25,000 GPUs per largest factory</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>Operational by end 2025-2026</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Foundation layer; Gigafactories are 3-4x larger than biggest AI Factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Mistral / Campus AI (parallel private)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>EUR 4bn+ Mistral infrastructure + Campus AI JV (Bpifrance/Nvidia/MGX) targeting 3 GW in France</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>200 MW Mistral capacity by 2027; 1.4 GW Campus AI pilot site</t>
+        </is>
+      </c>
+      <c r="E15" s="47" t="inlineStr">
+        <is>
+          <t>Construction H2 2026; operational 2028</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Private-led infrastructure moves faster than public programme; complements Gigafactories</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>CADA Additional Investment</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>EUR 200bn total for cloud/AI data centres (mostly private) per CADA impact assessment</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>EUR 200bn</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="inlineStr">
+        <is>
+          <t>2026-2036</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Gigafactories are anchor projects within broader CADA data centre tripling plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>FUNDING BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Total EU AI Infrastructure Investment (est.)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>EUR 230bn+ cumulative through 2035 (EUR 20bn AIGF + EUR 10bn AI Factories + EUR 200bn CADA)</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>EUR 230bn+</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>2021-2035</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Massive but still fraction of US private sector AI capex (~$300bn in 2026 alone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>AION Consortium (France)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Ardian, Artefact, Bull, Capgemini, EDF, Iliad/Scaleway, Orange</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="inlineStr">
+        <is>
+          <t>EUR 10bn; 200 MW initial (1 GW ultimate); 288,000 H100-equivalent GPUs</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>Bid submitted May 2026; decision expected Q4 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Largest single-country bid; end-to-end EU stack (energy, cloud, AI, integration); Scaleway provides sovereign cloud layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Spain (Telefonica-led)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Telefonica, ACS, Spanish government; site: Mora la Nova (Catalonia)</t>
+        </is>
+      </c>
+      <c r="D20" s="48" t="inlineStr">
+        <is>
+          <t>Multi-billion EUR bid; specifics not fully disclosed</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>Bid in preparation; formal submission 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Spain's energy advantages (solar) and grid capacity attract AI infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Germany (Hochtief/Ionos-led)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Hochtief, Ionos (United Internet), research institutions</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>Multi-billion EUR bid; location TBD</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>Bid in preparation</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>German industrial base and research ecosystem (Fraunhofer, DFKI) strengthen bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Netherlands (AI Gigafactory.NL)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Supported by Peter Wennink (ex-ASML CEO); industry and academic consortium</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="inlineStr">
+        <is>
+          <t>Multi-billion EUR bid; location TBD</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>Bid in preparation</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Netherlands' semiconductor ecosystem (ASML, NXP, Imec) creates unique synergies with chip-to-compute integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Other Bidders</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Finland, Italy, Portugal, Austria (Vienna), Czech Republic (Prague), Poland, and others</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>76 total expressions of interest across 60 sites in 16 Member States</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>Submitted June 2025</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Geographic spread ensures broad EU access but risks diluting compute concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="65" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN BIDS &amp; PROJECTS</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Campus AI (France - parallel)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Bpifrance, Mistral, Nvidia, MGX (UAE); pilot site at Fouju (Seine-et-Marne)</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>3 GW target across France; 1.4 GW initial site; EUR multi-billion</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>Construction H2 2026; operations 2028</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Separate from AIGF programme; Mistral gets priority compute access; sovereign cloud + exascale computing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>US AI Compute Capacity (2026)</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>~8,200 MW dedicated AI data centre capacity; 39.7M H100-equivalents</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>75% of global AI supercomputing power</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="inlineStr">
+        <is>
+          <t>Operational now</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>US adds more AI compute capacity each quarter than EU's entire installed base</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="inlineStr">
+        <is>
+          <t>EU AI Compute Capacity (2026)</t>
+        </is>
+      </c>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>~3,500 MW total (AI-specific ~2,000 MW); ~2.5M H100-equivalents</t>
+        </is>
+      </c>
+      <c r="D27" s="52" t="inlineStr">
+        <is>
+          <t>&lt;5% of global AI supercomputing power</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="inlineStr">
+        <is>
+          <t>Operational now</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>17x less AI computing power than US; comparable to a single US hyperscaler's 2024 deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="inlineStr">
+        <is>
+          <t>China AI Compute Capacity (2026)</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>~3,100 MW; constrained by US export controls on advanced chips</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>~15% of global capacity but falling</t>
+        </is>
+      </c>
+      <c r="E28" s="53" t="inlineStr">
+        <is>
+          <t>Operational now</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>China compensates with algorithmic efficiency (DeepSeek); EU lacks both hardware AND efficiency advantages</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="inlineStr">
+        <is>
+          <t>EU Post-Gigafactory Capacity (2032E)</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>~9,700 MW total by 2031; Gigafactories add 500-600K GPUs</t>
+        </is>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>EU share rises to ~8-10% of global AI compute</t>
+        </is>
+      </c>
+      <c r="E29" s="53" t="inlineStr">
+        <is>
+          <t>2030-2032</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Closes gap vs. 2025 US levels but US will have grown to ~26,400 MW by 2031; relative gap may widen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="inlineStr">
+        <is>
+          <t>Single US Company Comparison</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>xAI Colossus: 555,000 GPUs, 2 GW capacity; Meta: $115-135bn 2026 capex; Google: ~25% of global AI compute</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>Single US company exceeds entire EU AIGF programme</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="inlineStr">
+        <is>
+          <t>Operational 2025-2026</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>EU's EUR 20bn programme roughly equals what one US tech company spends in a single year</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>COMPUTE GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="inlineStr">
+        <is>
+          <t>Frontier Model Training Requirements</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>Current frontier models: 10,000-100,000+ GPUs for weeks/months; next-gen may require 500K+ GPUs</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>xAI Grok-4 used ~5x10^26 FLOPs; Llama 3 used 16,384 H100s for 54 days</t>
+        </is>
+      </c>
+      <c r="E31" s="53" t="inlineStr">
+        <is>
+          <t>Scaling rapidly</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Each EU Gigafactory (75K GPUs) can train one frontier model at a time; US labs run multiple in parallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Current EU LLM Position</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Mistral AI is only EU frontier model developer; $400M ARR; 60% revenue from Europe</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>EU has &lt;5% of global AI compute; Mistral trains on US cloud infrastructure (AWS/Azure) and own facility</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="inlineStr">
+        <is>
+          <t>As of mid-2026</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Without sovereign compute, EU's leading AI company remains dependent on US infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="65" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Gigafactory Compute for LLM Training</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Each AIGF (75K GPUs) sufficient for training one frontier-scale model at a time</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>7-8 facilities = 7-8 simultaneous frontier training runs possible</t>
+        </is>
+      </c>
+      <c r="E34" s="55" t="inlineStr">
+        <is>
+          <t>Operational 2030-2032</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>By 2030 standards, 75K GPUs may be entry-level for frontier training; continuous hardware refresh needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Democratised Access for EU Startups</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>AI Factory access modes: Playground (2 working days), Fast Lane (50K GPU-hours), Large Scale (&gt;50K GPU-hours)</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Free compute access for SMEs and startups; reduces US cloud dependency for EU AI ecosystem</t>
+        </is>
+      </c>
+      <c r="E35" s="55" t="inlineStr">
+        <is>
+          <t>AI Factories operational now; Gigafactories by 2030</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Lowers barrier to entry for EU AI startups; creates pipeline of companies beyond Mistral</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="65" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Sovereign Training Data Advantage</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Gigafactories will integrate with EU Common Data Spaces; 24 official EU languages; GDPR-compliant data governance</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>EU data spaces cover health, agriculture, manufacturing, energy, finance</t>
+        </is>
+      </c>
+      <c r="E36" s="55" t="inlineStr">
+        <is>
+          <t>Progressive; data spaces maturing 2026-2028</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>EU's multilingual, domain-specific data is a genuine advantage if Gigafactories enable its exploitation at scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="65" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>EU Open-Source Model Ecosystem</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>EU Open Source Strategy + CADA open-source-first procurement = demand pull for EU open-weight models</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>Mistral (Apache 2.0 models), Hugging Face (France/US), BLOOM legacy, LAION</t>
+        </is>
+      </c>
+      <c r="E37" s="55" t="inlineStr">
+        <is>
+          <t>Ongoing; CADA adoption Q2 2027</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Open-weight models + sovereign compute + open-source procurement = viable EU LLM ecosystem by 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="65" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Inference Infrastructure Gap</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>LLM inference (running models) will be 65% of AI compute spend by 2035; requires different infrastructure than training</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
+        <is>
+          <t>Gigafactories designed for training; inference needs distributed, edge-adjacent infrastructure</t>
+        </is>
+      </c>
+      <c r="E38" s="55" t="inlineStr">
+        <is>
+          <t>Inference demand scales with enterprise AI adoption</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>CADA's data centre tripling + sovereign cloud providers handle inference; Gigafactories handle training; EU needs BOTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Chip Sovereignty Linkage</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Gigafactories create anchor demand for EU-designed AI chips (Chips Act 2.0 Demand Accelerators)</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
+        <is>
+          <t>75K+ GPUs per facility x 7-8 facilities = 525-600K+ GPUs to procure</t>
+        </is>
+      </c>
+      <c r="E39" s="55" t="inlineStr">
+        <is>
+          <t>Foundry pilot 2030-2033</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Initially 100% NVIDIA; by 2033-2035, EU-designed chips (Axelera, SiPearl) could supply 10-15% of Gigafactory refreshes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="65" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Risk: Obsolescence by Arrival</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Formal call Summer 2026; construction 2028; operations 2030-2032; US frontier moves every 6-12 months</t>
+        </is>
+      </c>
+      <c r="D40" s="54" t="inlineStr">
+        <is>
+          <t>75K GPUs in 2030 may be equivalent to 2025 mid-tier US cluster</t>
+        </is>
+      </c>
+      <c r="E40" s="55" t="inlineStr">
+        <is>
+          <t>Continuous risk</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Must build in hardware refresh cycle (every 2-3 years) and modular architecture; EU procurement speed is critical weakness</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Risk: Brain Drain Continues</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>EU AI researchers leave for US labs offering 10-100x more compute and higher salaries</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>Stanford data: EU produced only 6% of notable AI models despite strong research base</t>
+        </is>
+      </c>
+      <c r="E41" s="55" t="inlineStr">
+        <is>
+          <t>Ongoing structural issue</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Gigafactories partially address compute gap but salary/funding gap remains; talent retention requires compute + funding + culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="65" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>IMPACT ON EU LLM LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Realistic EU LLM Position by 2035</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>EU could train 2-3 frontier-class models annually on sovereign infrastructure; serve 35-40% of EU enterprise LLM market</t>
+        </is>
+      </c>
+      <c r="D42" s="54" t="inlineStr">
+        <is>
+          <t>Requires: Gigafactories operational + Mistral/successors at frontier + open-source ecosystem + sovereign cloud adoption</t>
+        </is>
+      </c>
+      <c r="E42" s="55" t="inlineStr">
+        <is>
+          <t>2030-2035</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Not US-parity but sufficient for technological autonomy in EU-critical use cases (government, defence, industrial, healthcare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="65" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Phase 1: AI Factories (operational)</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>EUR 10bn (EU + Member States + associated countries); 19 facilities + 13 antennas</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t>EUR 10bn</t>
+        </is>
+      </c>
+      <c r="E44" s="57" t="inlineStr">
+        <is>
+          <t>2021-2027</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Foundation layer; largest factories ~25,000 GPUs; free access for startups/SMEs</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2: AI Gigafactories</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>EUR 20bn (EU 17% + Member States 17%+ + private ~66%)</t>
+        </is>
+      </c>
+      <c r="D45" s="56" t="inlineStr">
+        <is>
+          <t>EUR 20bn</t>
+        </is>
+      </c>
+      <c r="E45" s="57" t="inlineStr">
+        <is>
+          <t>2026-2032</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>7-8 facilities with 75,000+ GPUs each; frontier training capability</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="65" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Phase 3: CADA Data Centre Expansion</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>EUR 200bn (mostly private investment) to triple EU data centre capacity</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t>EUR 200bn</t>
+        </is>
+      </c>
+      <c r="E46" s="57" t="inlineStr">
+        <is>
+          <t>2026-2036</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Inference and deployment infrastructure; sovereign cloud scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Parallel: Private AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Mistral/Campus AI (~EUR 4-10bn), AION (EUR 10bn), hyperscaler EU capex (~EUR 40bn/year)</t>
+        </is>
+      </c>
+      <c r="D47" s="56" t="inlineStr">
+        <is>
+          <t>EUR 50-100bn+ cumulative private</t>
+        </is>
+      </c>
+      <c r="E47" s="57" t="inlineStr">
+        <is>
+          <t>2025-2035</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Private investment dwarfs public; but public sets sovereignty framework and standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="65" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Parallel: Chips Act 2.0 Semiconductor</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>EUR 120bn (public + private) for EU semiconductor ecosystem including AI chips</t>
+        </is>
+      </c>
+      <c r="D48" s="56" t="inlineStr">
+        <is>
+          <t>EUR 120bn</t>
+        </is>
+      </c>
+      <c r="E48" s="57" t="inlineStr">
+        <is>
+          <t>2026-2035</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Supplies the chips that go into Gigafactories; 3nm foundry + advanced packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>INVESTMENT SUMMARY: 2025-2035</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL ESTIMATED EU AI INFRASTRUCTURE INVESTMENT</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>EUR 350-450bn cumulative across all programmes and private investment through 2035</t>
+        </is>
+      </c>
+      <c r="D49" s="56" t="inlineStr">
+        <is>
+          <t>EUR 350-450bn</t>
+        </is>
+      </c>
+      <c r="E49" s="57" t="inlineStr">
+        <is>
+          <t>2021-2035</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Substantial but compare to US: single year 2026 private AI capex exceeds EUR 300bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="65" customHeight="1">
+      <c r="A51" s="58" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B51" s="58" t="inlineStr">
+        <is>
+          <t>Overall Verdict</t>
+        </is>
+      </c>
+      <c r="C51" s="59" t="inlineStr">
+        <is>
+          <t>EU AI Gigafactory programme is necessary but not sufficient for LLM leadership</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr"/>
+      <c r="E51" s="61" t="inlineStr">
+        <is>
+          <t>2030-2035</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>EU will not match US compute scale; goal should be 'strategic autonomy' not 'parity'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="65" customHeight="1">
+      <c r="A52" s="58" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B52" s="58" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="C52" s="59" t="inlineStr">
+        <is>
+          <t>Largest public AI infrastructure programme globally; strong private interest (76 bids); sovereign compute for EU-critical applications; open-source ecosystem (Mistral, Hugging Face); multilingual data advantage</t>
+        </is>
+      </c>
+      <c r="D52" s="60" t="inlineStr"/>
+      <c r="E52" s="61" t="inlineStr"/>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>These are genuine differentiators vs. US private-sector-dominated model</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="65" customHeight="1">
+      <c r="A53" s="58" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B53" s="58" t="inlineStr">
+        <is>
+          <t>Weaknesses</t>
+        </is>
+      </c>
+      <c r="C53" s="59" t="inlineStr">
+        <is>
+          <t>3-4 year deployment lag vs. US; 75K GPUs/facility may be outdated by arrival; procurement complexity; energy bottleneck; talent retention; no EU AI chip for initial deployment; single frontier model developer (Mistral)</t>
+        </is>
+      </c>
+      <c r="D53" s="60" t="inlineStr"/>
+      <c r="E53" s="61" t="inlineStr"/>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Speed of execution is the make-or-break factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="65" customHeight="1">
+      <c r="A54" s="58" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B54" s="58" t="inlineStr">
+        <is>
+          <t>Key Success Metrics by 2035</t>
+        </is>
+      </c>
+      <c r="C54" s="59" t="inlineStr">
+        <is>
+          <t>(1) 7-8 Gigafactories operational with current-gen hardware; (2) 2+ EU frontier LLM developers; (3) 35-40% of EU enterprise LLM market served by EU models; (4) 10-15% of Gigafactory GPUs EU-designed; (5) EU LLM used in all 27 Member State governments</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="inlineStr"/>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>If all 5 metrics met, EU achieves meaningful LLM sovereignty; if &lt;3, programme has underdelivered</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F54"/>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
+++ b/EU_Chips_Act_2.0_Dependency_Analysis.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dependency Analysis'!$A$1:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Market Sizing &amp; EU Revenue'!$A$1:$Q$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI Gigafactory &amp; LLM Impact'!$A$1:$F$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI Gigafactory &amp; LLM Impact'!$A$1:$F$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,7 +93,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -198,6 +198,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFD7D7"/>
+        <bgColor rgb="00FFD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8CC"/>
+        <bgColor rgb="00FFE8CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
         <bgColor rgb="00D9E2F3"/>
       </patternFill>
@@ -229,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -279,13 +291,13 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -412,6 +424,42 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2158,7 +2206,7 @@
           <t>Original Chips Act introduced crisis response mechanism; Chips Act 2.0 strengthens with proactive tools; 2025 simulation exercise with member states conducted</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Improvement over original, but untested in real crisis</t>
         </is>
@@ -2325,184 +2373,184 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>HEADLINE STATISTICS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>EU share of global semiconductor production</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>~10%</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Down from historic highs; virtually no leading-edge AI chips</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>EU cloud market share held by EU providers</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>~15%</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Stable since 2022; down from 29% in 2017</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr"/>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>US hyperscaler share of EU cloud market</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>~70%</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>AWS + Azure + GCP combined</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>EU dependency on chip imports</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>78% of EUR 55bn consumption (2024)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>EUR 43.6bn imported from third countries</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>AI components share of semiconductor market by 2030</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>&gt;70%</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>AI logic chips CAGR 18-29% (2023-2030)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Total investment needed for tech sovereignty</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>EUR 320bn over 10 years</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>EUR 120bn semiconductors + EUR 200bn cloud/AI + EUR 20bn energy AI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Advanced foundry investment</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>EUR 30bn</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>For first EU 3nm-and-below open foundry</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>EU data centre capacity target</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Triple current capacity by 2031-2033</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Currently 3.6 GW FLAP-D colocation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>EuroHPC infrastructure</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>14 supercomputers, 19 AI Factories, 10 quantum systems</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>EUR 7bn budget</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>DEPENDENCY HEAT MAP BY AREA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr"/>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Cloud - Infrastructure Market Share</t>
         </is>
@@ -2512,15 +2560,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>US dominance structurally entrenched; EUR 10bn/quarter US capex in EU</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Cloud - Sovereignty &amp; Data Control</t>
         </is>
@@ -2530,15 +2578,15 @@
           <t>4 - High</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>CADA SEAL framework proposed but not yet law; EUR 180m sovereign cloud tender awarded</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr"/>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Cloud - Hardware Supply Chain</t>
         </is>
@@ -2548,15 +2596,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>No EU-designed server processors or AI GPUs at scale</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr"/>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>AI Datacenters - Capacity</t>
         </is>
@@ -2566,15 +2614,15 @@
           <t>4 - High</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Energy is binding constraint; Ireland at 22% electricity consumption</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>AI Datacenters - GPU/Accelerator</t>
         </is>
@@ -2584,15 +2632,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>NVIDIA &gt;80% market; EU has only pre-scale startups</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr"/>
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>AI Datacenters - Chip Design Ecosystem</t>
         </is>
@@ -2602,15 +2650,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>US EDA tools (Synopsys/Cadence) monopoly; no scaled EU fabless AI companies</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr"/>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>AI Datacenters - Advanced Packaging</t>
         </is>
@@ -2620,15 +2668,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Most significant near-term structural gap; TSMC CoWoS dominance</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr"/>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr"/>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>LLMs - Training Compute</t>
         </is>
@@ -2638,15 +2686,15 @@
           <t>4 - High</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>EU AI labs train on US cloud; Gigafactory programme aims to close gap</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr"/>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr"/>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>LLMs - Inference Chips</t>
         </is>
@@ -2656,15 +2704,15 @@
           <t>4 - High</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>EU has emerging low-power strengths but no scaled inference accelerator</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr"/>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr"/>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>LLMs - Software/Model Sovereignty</t>
         </is>
@@ -2674,15 +2722,15 @@
           <t>3 - Moderate</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Mistral AI is bright spot; but US models dominate enterprise deployment</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr"/>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr"/>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>LLMs - Memory &amp; Interconnect</t>
         </is>
@@ -2692,15 +2740,15 @@
           <t>5 - Critical</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>HBM monopoly (SK Hynix/Samsung/Micron); NVLink/InfiniBand (NVIDIA)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr"/>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr"/>
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Quantum - Chip Development</t>
         </is>
@@ -2710,15 +2758,15 @@
           <t>2 - Moderate</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Strong R&amp;D with 6 pilot lines; lab-to-fab gap remains</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr"/>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr"/>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Quantum - Photonics</t>
         </is>
@@ -2728,15 +2776,15 @@
           <t>3 - Moderate</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>PIXEurope telecom-focused; quantum needs visible/UV range expansion</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr"/>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr"/>
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Quantum - Enabling Electronics</t>
         </is>
@@ -2746,15 +2794,15 @@
           <t>3 - Moderate</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>Chips JU EUR 20m call addresses gap; Bluefors (Finland) is global cryogenics leader</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr"/>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr"/>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Quantum - Hybrid Infrastructure</t>
         </is>
@@ -2764,15 +2812,15 @@
           <t>3 - Moderate</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>EuroHPC integrating quantum; but cloud access via US platforms</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Quantum - PQC Readiness</t>
         </is>
@@ -2782,679 +2830,679 @@
           <t>2 - Moderate</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>EU strength in security chips (NXP, Infineon); PQC transition manageable</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>KEY EU STRENGTHS TO LEVERAGE</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr"/>
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Lithography equipment</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>ASML global EUV monopoly</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Geopolitical leverage; indispensable node in value chain</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Power/automotive/industrial chips</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>NXP, Infineon, STMicroelectronics, Bosch</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Mainstream chips; wide-bandgap semiconductors (SiC, GaN)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Semiconductor R&amp;D</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Imec, Fraunhofer, CEA-Leti</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>World-class research; pilot line experience</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr"/>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr"/>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>EUV optics</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>Zeiss (Germany)</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Critical ASML supply chain partner</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr"/>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr"/>
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>SOI substrates</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>SOITEC (France)</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Global leader in silicon-on-insulator</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr"/>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr"/>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Quantum hardware diversity</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>IQM, Pasqal, QuiX, AQT + 6 pilot lines</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Multiple qubit modalities; strong academic base</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr"/>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr"/>
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Cryogenics</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>Bluefors (Finland)</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Global leader in dilution refrigerators for quantum</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr"/>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr"/>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>AI models (open-weight)</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Mistral AI (France)</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Leading European frontier model developer</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr"/>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr"/>
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Security/identity chips</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>NXP, Infineon</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Strong position for PQC transition</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>CRITICAL GAPS REQUIRING ACTION</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr"/>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr"/>
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Leading-edge foundry (sub-5nm)</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>None in EU</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Fully dependent on TSMC (Taiwan) and Samsung (Korea); pilot production 2030-2033 at earliest</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr"/>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr"/>
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>AI GPU/accelerator design</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>No scaled EU company</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>NVIDIA/AMD monopoly; EU startups (Axelera, SiPearl) pre-revenue or early-revenue</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr"/>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr"/>
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>High Bandwidth Memory (HBM)</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>No EU production</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>SK Hynix, Samsung, Micron control entire market</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr"/>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr"/>
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>Advanced packaging at scale</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>No EU facility</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>TSMC CoWoS, ASE, Amkor dominate; EU foundry plans include 3D packaging</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr"/>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr"/>
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>EDA tools</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>No EU equivalent</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>Synopsys, Cadence, Siemens EDA (German-headquartered but US-listed)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="inlineStr"/>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr"/>
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>Cloud platform services</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>15% EU market share</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Structural scale disadvantage vs. hyperscalers; unlikely to close gap significantly</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="inlineStr"/>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr"/>
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>AI training compute clusters</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>Insufficient scale</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Largest EU clusters far smaller than US frontier lab clusters (100k+ GPUs)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>CHIPS ACT 2.0 - KEY POLICY INSTRUMENTS</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="inlineStr"/>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr"/>
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Demand Accelerators</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>Public innovation procurement; demand aggregation; forum for EU chip uptake</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Shift from supply-only to supply+demand strategy</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="inlineStr"/>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr"/>
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Strategic Projects</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>Facilitated public investment; fast-track permitting (12-month max); State aid simplification</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Covers entire value chain: materials to packaging</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr"/>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr"/>
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>EU Open Foundry</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>First EU 3nm-and-below fab with chiplet + 3D packaging</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>EUR 30bn investment; pilot 2030-2033</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr"/>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr"/>
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Grand Challenges</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>Industrial development of strategically important chips (esp. AI)</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Competition-based funding mechanism</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr"/>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr"/>
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Chips Fund</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>Debt financing and equity for semiconductor startups/scaleups/SMEs</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Addressing EU venture capital gap in deep tech</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="inlineStr"/>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr"/>
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>B2B Supply Chain Platform</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>Real-time visibility into semiconductor supply chains</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>Crisis preparedness; proactive risk management</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr"/>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr"/>
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>Semiconductor Regions of Excellence</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>Label for regions creating framework conditions for semiconductor investment</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Attracting and concentrating investment</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr"/>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr"/>
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Strategic Partnerships</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>International cooperation on semiconductors with like-minded partners</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Diversifying supply away from single-source dependencies</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>LEGISLATIVE TIMELINE</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="inlineStr"/>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr"/>
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Chips Act 2.0 proposal published</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>3 June 2026</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>COM(2026) 503</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="inlineStr"/>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr"/>
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>CADA proposal published</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>3 June 2026</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>COM(2026) 502</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr"/>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="A59" s="18" t="inlineStr"/>
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>EU Open Source Strategy published</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>3 June 2026</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Non-legislative</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="inlineStr"/>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="A60" s="18" t="inlineStr"/>
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>Quantum-enabling technology call</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C60" s="18" t="inlineStr">
         <is>
           <t>Jul-Sep 2026</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>EUR 20m; Chips JU</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="inlineStr"/>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="A61" s="18" t="inlineStr"/>
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>AI Gigafactory call</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
         <is>
           <t>Expected July 2026</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Under CADA</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="inlineStr"/>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr"/>
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>National Digital Decade Roadmap revisions</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C62" s="18" t="inlineStr">
         <is>
           <t>December 2026</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Member state action</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="inlineStr"/>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="A63" s="18" t="inlineStr"/>
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>EU semiconductor crisis management Blueprint</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr"/>
+      <c r="D63" s="19" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="inlineStr"/>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="A64" s="18" t="inlineStr"/>
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>Final adoption target (Chips Act 2.0 + CADA)</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Subject to Parliament and Council negotiation</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="19" t="inlineStr"/>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="A65" s="18" t="inlineStr"/>
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>Advanced foundry pilot production</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
+      <c r="C65" s="18" t="inlineStr">
         <is>
           <t>2030-2033</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Subject to investment mobilisation</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="inlineStr"/>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="A66" s="18" t="inlineStr"/>
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Data centre capacity tripled</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>2031-2033</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>CADA target</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="19" t="inlineStr"/>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="A67" s="18" t="inlineStr"/>
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Full semiconductor investment mobilisation</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>By 2035</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>EUR 120bn public+private</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="19" t="inlineStr"/>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="A68" s="18" t="inlineStr"/>
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>Data centre investment complete</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>By 2036</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>EUR 200bn public+private</t>
         </is>
@@ -4680,7 +4728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6108,122 +6156,1138 @@
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="43" t="inlineStr">
         <is>
-          <t>ASSESSMENT</t>
+          <t>US vs EU CAPACITY: TRAINING</t>
         </is>
       </c>
     </row>
     <row r="51" ht="65" customHeight="1">
       <c r="A51" s="58" t="inlineStr">
         <is>
-          <t>ASSESSMENT</t>
+          <t>US vs EU CAPACITY: TRAINING</t>
         </is>
       </c>
       <c r="B51" s="58" t="inlineStr">
         <is>
-          <t>Overall Verdict</t>
+          <t>US Total AI Data Centre Capacity (2025)</t>
         </is>
       </c>
       <c r="C51" s="59" t="inlineStr">
         <is>
-          <t>EU AI Gigafactory programme is necessary but not sufficient for LLM leadership</t>
-        </is>
-      </c>
-      <c r="D51" s="60" t="inlineStr"/>
+          <t>~30 GW total DC; ~8.2 GW dedicated AI; 39.7M H100-equivalents</t>
+        </is>
+      </c>
+      <c r="D51" s="60" t="inlineStr">
+        <is>
+          <t>8,200 MW AI-dedicated</t>
+        </is>
+      </c>
       <c r="E51" s="61" t="inlineStr">
         <is>
-          <t>2030-2035</t>
+          <t>2025 actual</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>EU will not match US compute scale; goal should be 'strategic autonomy' not 'parity'</t>
+          <t>US hosts 75% of global AI supercomputing power; 17x more AI compute than EU</t>
         </is>
       </c>
     </row>
     <row r="52" ht="65" customHeight="1">
       <c r="A52" s="58" t="inlineStr">
         <is>
-          <t>ASSESSMENT</t>
+          <t>US vs EU CAPACITY: TRAINING</t>
         </is>
       </c>
       <c r="B52" s="58" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>US Total AI Data Centre Capacity (2030E)</t>
         </is>
       </c>
       <c r="C52" s="59" t="inlineStr">
         <is>
-          <t>Largest public AI infrastructure programme globally; strong private interest (76 bids); sovereign compute for EU-critical applications; open-source ecosystem (Mistral, Hugging Face); multilingual data advantage</t>
-        </is>
-      </c>
-      <c r="D52" s="60" t="inlineStr"/>
-      <c r="E52" s="61" t="inlineStr"/>
+          <t>80-90 GW total DC; ~62 GW AI training + 93 GW inference (McKinsey); Deloitte: 80 GW AI-specific</t>
+        </is>
+      </c>
+      <c r="D52" s="60" t="inlineStr">
+        <is>
+          <t>62,200 MW training / 93,300 MW inference</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>These are genuine differentiators vs. US private-sector-dominated model</t>
+          <t>US adds ~14 GW new compute in 2026 alone; 20+ GW in 2027 (Morgan Stanley)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="65" customHeight="1">
       <c r="A53" s="58" t="inlineStr">
         <is>
-          <t>ASSESSMENT</t>
+          <t>US vs EU CAPACITY: TRAINING</t>
         </is>
       </c>
       <c r="B53" s="58" t="inlineStr">
         <is>
-          <t>Weaknesses</t>
+          <t>US Total AI Data Centre Capacity (2035E)</t>
         </is>
       </c>
       <c r="C53" s="59" t="inlineStr">
         <is>
-          <t>3-4 year deployment lag vs. US; 75K GPUs/facility may be outdated by arrival; procurement complexity; energy bottleneck; talent retention; no EU AI chip for initial deployment; single frontier model developer (Mistral)</t>
-        </is>
-      </c>
-      <c r="D53" s="60" t="inlineStr"/>
-      <c r="E53" s="61" t="inlineStr"/>
+          <t>123 GW AI DC (Deloitte US outlook); total DC could exceed 150 GW; 1/3 of campuses exceed 1 GW</t>
+        </is>
+      </c>
+      <c r="D53" s="60" t="inlineStr">
+        <is>
+          <t>~123,000 MW AI-dedicated</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Speed of execution is the make-or-break factor</t>
+          <t>30x growth from 2024's 4 GW; mega-training campuses at multi-GW scale become standard</t>
         </is>
       </c>
     </row>
     <row r="54" ht="65" customHeight="1">
       <c r="A54" s="58" t="inlineStr">
         <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B54" s="58" t="inlineStr">
+        <is>
+          <t>Stargate (OpenAI/Oracle/SoftBank)</t>
+        </is>
+      </c>
+      <c r="C54" s="59" t="inlineStr">
+        <is>
+          <t>$500bn over 4 years; ~7 GW planned (May 2026); 10 GW target by 2029; 2M GPUs; 8+ sites across US</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="inlineStr">
+        <is>
+          <t>7,000-10,000 MW</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr">
+        <is>
+          <t>Abilene TX live; full 10 GW by 2029</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Single project exceeds entire EU Gigafactory programme; GPT-5.5 trained at Abilene</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="65" customHeight="1">
+      <c r="A55" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B55" s="58" t="inlineStr">
+        <is>
+          <t>xAI Colossus (Memphis TN)</t>
+        </is>
+      </c>
+      <c r="C55" s="59" t="inlineStr">
+        <is>
+          <t>555,000 GPUs; 2 GW total capacity; Colossus I (300 MW live) + Colossus II (1 GW under construction)</t>
+        </is>
+      </c>
+      <c r="D55" s="60" t="inlineStr">
+        <is>
+          <t>2,000 MW</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr">
+        <is>
+          <t>Colossus I live; II construction 2026</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Built in 122 days; faster than any EU procurement cycle; Grok-4 trained here</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="65" customHeight="1">
+      <c r="A56" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B56" s="58" t="inlineStr">
+        <is>
+          <t>Meta Hyperion (Louisiana)</t>
+        </is>
+      </c>
+      <c r="C56" s="59" t="inlineStr">
+        <is>
+          <t>7.5 GW gas-fired campus; $115-135bn 2026 capex; millions of Blackwell + AMD GPUs on order</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="inlineStr">
+        <is>
+          <t>7,500 MW planned</t>
+        </is>
+      </c>
+      <c r="E56" s="61" t="inlineStr">
+        <is>
+          <t>Under development</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Single Meta campus = 2x entire EU Gigafactory programme; Llama models trained here</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="65" customHeight="1">
+      <c r="A57" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B57" s="58" t="inlineStr">
+        <is>
+          <t>Google AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C57" s="59" t="inlineStr">
+        <is>
+          <t>~25% of global AI compute; 7 GW new capacity in 2027; $175-185bn 2026 capex; TPU v6 + NVIDIA</t>
+        </is>
+      </c>
+      <c r="D57" s="60" t="inlineStr">
+        <is>
+          <t>7,000 MW new in 2027 alone</t>
+        </is>
+      </c>
+      <c r="E57" s="61" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Google's annual capex (~$180bn) exceeds EU's entire cumulative AIGF programme (EUR 20bn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="65" customHeight="1">
+      <c r="A58" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B58" s="58" t="inlineStr">
+        <is>
+          <t>Microsoft AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>5 GW new capacity in 2027; $110-120bn 2026 capex; Azure + Stargate partnership</t>
+        </is>
+      </c>
+      <c r="D58" s="60" t="inlineStr">
+        <is>
+          <t>5,000 MW new in 2027</t>
+        </is>
+      </c>
+      <c r="E58" s="61" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Also expanding EU sovereign cloud (Brandenburg); dual US/EU strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="65" customHeight="1">
+      <c r="A59" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B59" s="58" t="inlineStr">
+        <is>
+          <t>Amazon/AWS AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C59" s="59" t="inlineStr">
+        <is>
+          <t>$200bn 2026 capex (largest single company); 5 GW new in 2027; Trainium custom chips</t>
+        </is>
+      </c>
+      <c r="D59" s="60" t="inlineStr">
+        <is>
+          <t>5,000 MW new in 2027</t>
+        </is>
+      </c>
+      <c r="E59" s="61" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>AWS also operates EU sovereign cloud; Trainium reduces NVIDIA dependence</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="65" customHeight="1">
+      <c r="A60" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B60" s="58" t="inlineStr">
+        <is>
+          <t>US Big 4 Combined 2026 Capex</t>
+        </is>
+      </c>
+      <c r="C60" s="59" t="inlineStr">
+        <is>
+          <t>$630bn combined (Amazon $200bn + Google $180bn + Meta $125bn + Microsoft $115bn); 62% increase YoY</t>
+        </is>
+      </c>
+      <c r="D60" s="60" t="inlineStr">
+        <is>
+          <t>$630bn in single year</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>US Big 4's single-year capex = ~30x EU's total AIGF programme budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="65" customHeight="1">
+      <c r="A61" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B61" s="58" t="inlineStr">
+        <is>
+          <t>US Training Capacity Summary (2030)</t>
+        </is>
+      </c>
+      <c r="C61" s="59" t="inlineStr">
+        <is>
+          <t>~62 GW dedicated to AI training (McKinsey); 10+ mega-training campuses at GW+ scale</t>
+        </is>
+      </c>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>62,200 MW training</t>
+        </is>
+      </c>
+      <c r="E61" s="61" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>Sufficient for dozens of simultaneous frontier model training runs; EU can do 7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="65" customHeight="1">
+      <c r="A62" s="58" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: TRAINING</t>
+        </is>
+      </c>
+      <c r="B62" s="58" t="inlineStr">
+        <is>
+          <t>US Training Capacity Summary (2035E)</t>
+        </is>
+      </c>
+      <c r="C62" s="59" t="inlineStr">
+        <is>
+          <t>Extrapolating Deloitte trajectory: ~45-55 GW training (of 123 GW total AI); inference dominates but training still massive</t>
+        </is>
+      </c>
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>45,000-55,000 MW training</t>
+        </is>
+      </c>
+      <c r="E62" s="61" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Even as inference grows to 65-75% of spend, US training capacity alone exceeds entire EU DC estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="65" customHeight="1">
+      <c r="A64" s="62" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>US Inference Capacity (2025)</t>
+        </is>
+      </c>
+      <c r="C64" s="63" t="inlineStr">
+        <is>
+          <t>~20.9 GW AI inference (McKinsey); inference = 58.6% of AI infra spend (Futurum); growing fastest</t>
+        </is>
+      </c>
+      <c r="D64" s="64" t="inlineStr">
+        <is>
+          <t>20,900 MW inference</t>
+        </is>
+      </c>
+      <c r="E64" s="65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Inference overtook training as primary AI compute spend in early 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="65" customHeight="1">
+      <c r="A65" s="62" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>US Inference Capacity (2030E)</t>
+        </is>
+      </c>
+      <c r="C65" s="63" t="inlineStr">
+        <is>
+          <t>~93.3 GW AI inference (McKinsey); 72% of AI infra spend by 2030 (Futurum base case)</t>
+        </is>
+      </c>
+      <c r="D65" s="64" t="inlineStr">
+        <is>
+          <t>93,300 MW inference</t>
+        </is>
+      </c>
+      <c r="E65" s="65" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Inference grows 4.5x while training grows 2.7x; distributed regional hubs complement mega-campuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="65" customHeight="1">
+      <c r="A66" s="62" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+      <c r="B66" s="62" t="inlineStr">
+        <is>
+          <t>US Inference Capacity (2035E)</t>
+        </is>
+      </c>
+      <c r="C66" s="63" t="inlineStr">
+        <is>
+          <t>Extrapolating: ~70-80 GW inference (of 123 GW total AI); ABI Research: &gt;45 GW cloud AI inference alone</t>
+        </is>
+      </c>
+      <c r="D66" s="64" t="inlineStr">
+        <is>
+          <t>70,000-80,000 MW inference</t>
+        </is>
+      </c>
+      <c r="E66" s="65" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise AI adoption at 80%+; agentic workloads drive 24x token growth (Goldman Sachs); edge inference expands</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="65" customHeight="1">
+      <c r="A67" s="62" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+      <c r="B67" s="62" t="inlineStr">
+        <is>
+          <t>Inference Workload Shift</t>
+        </is>
+      </c>
+      <c r="C67" s="63" t="inlineStr">
+        <is>
+          <t>Training: one-time capital event; Inference: recurring operating expense scaling with success; 80-90% of model lifecycle compute goes to inference</t>
+        </is>
+      </c>
+      <c r="D67" s="64" t="inlineStr">
+        <is>
+          <t>Training ~28% / Inference ~72% of spend by 2030</t>
+        </is>
+      </c>
+      <c r="E67" s="65" t="inlineStr">
+        <is>
+          <t>Structural shift 2025-2030</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>EU's Gigafactories are designed for TRAINING; inference requires different distributed infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="65" customHeight="1">
+      <c r="A68" s="62" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: INFERENCE</t>
+        </is>
+      </c>
+      <c r="B68" s="62" t="inlineStr">
+        <is>
+          <t>Inference Architecture Difference</t>
+        </is>
+      </c>
+      <c r="C68" s="63" t="inlineStr">
+        <is>
+          <t>Mega training: centralised GW campuses; Inference: distributed 20-100 MW regional hubs + &lt;10 MW edge nodes</t>
+        </is>
+      </c>
+      <c r="D68" s="64" t="inlineStr">
+        <is>
+          <t>3 tiers: mega-campus / regional hub / edge node</t>
+        </is>
+      </c>
+      <c r="E68" s="65" t="inlineStr">
+        <is>
+          <t>2030-2035</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>EU's CADA tripling (data centres) addresses inference better than Gigafactories; sovereign cloud is inference play</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="43" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="65" customHeight="1">
+      <c r="A70" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B70" s="66" t="inlineStr">
+        <is>
+          <t>EU Total AI Data Centre Capacity (2025)</t>
+        </is>
+      </c>
+      <c r="C70" s="67" t="inlineStr">
+        <is>
+          <t>~10 GW total DC; ~3.5 GW dedicated AI (2026); ~2.5M H100-equivalents; ~2 GW AI power capacity</t>
+        </is>
+      </c>
+      <c r="D70" s="68" t="inlineStr">
+        <is>
+          <t>3,500 MW AI-dedicated (2026)</t>
+        </is>
+      </c>
+      <c r="E70" s="69" t="inlineStr">
+        <is>
+          <t>2025-2026 actual</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>EU has &lt;5% of global AI compute; 1.6 GW absorption in 2025 vs 17 GW in US</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="65" customHeight="1">
+      <c r="A71" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B71" s="66" t="inlineStr">
+        <is>
+          <t>EU Total DC Capacity (2030E)</t>
+        </is>
+      </c>
+      <c r="C71" s="67" t="inlineStr">
+        <is>
+          <t>~35 GW total (Affinius Capital); ~9.7 GW AI-specific (xpert.digital); CADA target: triple from ~10 GW to ~30 GW</t>
+        </is>
+      </c>
+      <c r="D71" s="68" t="inlineStr">
+        <is>
+          <t>9,700 MW AI-dedicated</t>
+        </is>
+      </c>
+      <c r="E71" s="69" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>CADA tripling on track would reach ~30 GW total; AI-specific ~10 GW; still 1/6 of US</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="65" customHeight="1">
+      <c r="A72" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B72" s="66" t="inlineStr">
+        <is>
+          <t>EU Total DC Capacity (2035E)</t>
+        </is>
+      </c>
+      <c r="C72" s="67" t="inlineStr">
+        <is>
+          <t>~50-60 GW total if CADA targets met + continued growth; AI-specific ~15-20 GW</t>
+        </is>
+      </c>
+      <c r="D72" s="68" t="inlineStr">
+        <is>
+          <t>15,000-20,000 MW AI-dedicated</t>
+        </is>
+      </c>
+      <c r="E72" s="69" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>EU reaches roughly 2030 US levels by 2035; 5-year structural lag persists</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="65" customHeight="1">
+      <c r="A73" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B73" s="66" t="inlineStr">
+        <is>
+          <t>AI Gigafactories (sovereign training)</t>
+        </is>
+      </c>
+      <c r="C73" s="67" t="inlineStr">
+        <is>
+          <t>7-8 facilities x 75,000+ GPUs = 525-600K GPUs; estimated ~3-5 GW combined compute capacity</t>
+        </is>
+      </c>
+      <c r="D73" s="68" t="inlineStr">
+        <is>
+          <t>3,000-5,000 MW (est.)</t>
+        </is>
+      </c>
+      <c r="E73" s="69" t="inlineStr">
+        <is>
+          <t>Operational 2030-2032</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Dedicated sovereign training capacity; can train 7-8 frontier models simultaneously</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="65" customHeight="1">
+      <c r="A74" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B74" s="66" t="inlineStr">
+        <is>
+          <t>AI Factories (existing sovereign)</t>
+        </is>
+      </c>
+      <c r="C74" s="67" t="inlineStr">
+        <is>
+          <t>19 factories + 13 antennas; largest ~25,000 GPUs; ~500-800 MW combined</t>
+        </is>
+      </c>
+      <c r="D74" s="68" t="inlineStr">
+        <is>
+          <t>500-800 MW</t>
+        </is>
+      </c>
+      <c r="E74" s="69" t="inlineStr">
+        <is>
+          <t>Operational 2025-2026</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Foundation layer; free access for startups; smaller than Gigafactories</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="65" customHeight="1">
+      <c r="A75" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B75" s="66" t="inlineStr">
+        <is>
+          <t>Campus AI / Mistral (sovereign private)</t>
+        </is>
+      </c>
+      <c r="C75" s="67" t="inlineStr">
+        <is>
+          <t>3 GW target in France (Bpifrance/Mistral/Nvidia/MGX); 200 MW Mistral by 2027; 1.4 GW pilot site</t>
+        </is>
+      </c>
+      <c r="D75" s="68" t="inlineStr">
+        <is>
+          <t>1,400-3,000 MW</t>
+        </is>
+      </c>
+      <c r="E75" s="69" t="inlineStr">
+        <is>
+          <t>Construction 2026; operations 2028</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Largest single EU sovereign compute project; Mistral priority access</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="65" customHeight="1">
+      <c r="A76" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B76" s="66" t="inlineStr">
+        <is>
+          <t>AION Consortium (if selected)</t>
+        </is>
+      </c>
+      <c r="C76" s="67" t="inlineStr">
+        <is>
+          <t>200 MW initial; 1 GW ultimate; 288K H100-equivalents; end-to-end EU stack</t>
+        </is>
+      </c>
+      <c r="D76" s="68" t="inlineStr">
+        <is>
+          <t>200-1,000 MW</t>
+        </is>
+      </c>
+      <c r="E76" s="69" t="inlineStr">
+        <is>
+          <t>Decision Q4 2026; construction 2028</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>May overlap with or complement Gigafactory programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="65" customHeight="1">
+      <c r="A77" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B77" s="66" t="inlineStr">
+        <is>
+          <t>US Hyperscaler Capex in EU</t>
+        </is>
+      </c>
+      <c r="C77" s="67" t="inlineStr">
+        <is>
+          <t>AWS/Azure/GCP invest ~EUR 40bn/year in EU infrastructure; AWS Sovereign Cloud (Brandenburg); Azure sovereign</t>
+        </is>
+      </c>
+      <c r="D77" s="68" t="inlineStr">
+        <is>
+          <t>~5-8 GW added by US companies in EU by 2030</t>
+        </is>
+      </c>
+      <c r="E77" s="69" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Non-sovereign but physically in EU; CADA SEAL framework governs access for public sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="65" customHeight="1">
+      <c r="A78" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B78" s="66" t="inlineStr">
+        <is>
+          <t>EU Sovereign AI Compute (2030E total)</t>
+        </is>
+      </c>
+      <c r="C78" s="67" t="inlineStr">
+        <is>
+          <t>Gigafactories (~4 GW) + AI Factories (~0.8 GW) + Campus AI (~1.5 GW) + sovereign cloud (~1 GW)</t>
+        </is>
+      </c>
+      <c r="D78" s="68" t="inlineStr">
+        <is>
+          <t>~7,000-8,000 MW sovereign</t>
+        </is>
+      </c>
+      <c r="E78" s="69" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Sovereign = EU-controlled and operated; ~20-25% of total EU AI DC capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="65" customHeight="1">
+      <c r="A79" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B79" s="66" t="inlineStr">
+        <is>
+          <t>EU Sovereign AI Compute (2035E total)</t>
+        </is>
+      </c>
+      <c r="C79" s="67" t="inlineStr">
+        <is>
+          <t>Gigafactories (refreshed ~5 GW) + Campus AI (~3 GW) + sovereign cloud (~3 GW) + new private (~4 GW)</t>
+        </is>
+      </c>
+      <c r="D79" s="68" t="inlineStr">
+        <is>
+          <t>~12,000-15,000 MW sovereign</t>
+        </is>
+      </c>
+      <c r="E79" s="69" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Sovereign compute reaches ~25-30% of EU AI capacity; remainder via US hyperscalers under SEAL framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="65" customHeight="1">
+      <c r="A80" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B80" s="66" t="inlineStr">
+        <is>
+          <t>EU Training vs Inference Split (2030E)</t>
+        </is>
+      </c>
+      <c r="C80" s="67" t="inlineStr">
+        <is>
+          <t>Training: ~4-5 GW (Gigafactories + AI Factories); Inference: ~5-6 GW (CADA data centres + sovereign cloud)</t>
+        </is>
+      </c>
+      <c r="D80" s="68" t="inlineStr">
+        <is>
+          <t>Training ~4.5 GW / Inference ~5.5 GW sovereign</t>
+        </is>
+      </c>
+      <c r="E80" s="69" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Training is Gigafactory focus; inference served by CADA-expanded DCs and sovereign cloud providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="65" customHeight="1">
+      <c r="A81" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B81" s="66" t="inlineStr">
+        <is>
+          <t>EU Training vs Inference Split (2035E)</t>
+        </is>
+      </c>
+      <c r="C81" s="67" t="inlineStr">
+        <is>
+          <t>Training: ~5-7 GW (refreshed Gigafactories + new capacity); Inference: ~8-12 GW (CADA + sovereign cloud scale-up)</t>
+        </is>
+      </c>
+      <c r="D81" s="68" t="inlineStr">
+        <is>
+          <t>Training ~6 GW / Inference ~10 GW sovereign</t>
+        </is>
+      </c>
+      <c r="E81" s="69" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Inference dominates EU sovereign compute by 2035 as enterprise AI adoption scales</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="65" customHeight="1">
+      <c r="A82" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B82" s="66" t="inlineStr">
+        <is>
+          <t>EU vs US Gap Summary (2030)</t>
+        </is>
+      </c>
+      <c r="C82" s="67" t="inlineStr">
+        <is>
+          <t>US training: ~62 GW vs EU sovereign training: ~4.5 GW = 14:1 gap; US inference: ~93 GW vs EU sovereign inference: ~5.5 GW = 17:1 gap</t>
+        </is>
+      </c>
+      <c r="D82" s="68" t="inlineStr">
+        <is>
+          <t>US leads 14-17x in both training and inference</t>
+        </is>
+      </c>
+      <c r="E82" s="69" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Gap narrows from 17x (2026) to 14x (2030) but remains massive; EU compensates with open-source efficiency and domain focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="65" customHeight="1">
+      <c r="A83" s="66" t="inlineStr">
+        <is>
+          <t>US vs EU CAPACITY: EU SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B83" s="66" t="inlineStr">
+        <is>
+          <t>EU vs US Gap Summary (2035)</t>
+        </is>
+      </c>
+      <c r="C83" s="67" t="inlineStr">
+        <is>
+          <t>US training: ~50 GW vs EU sovereign training: ~6 GW = 8:1 gap; US inference: ~75 GW vs EU sovereign inference: ~10 GW = 7.5:1 gap</t>
+        </is>
+      </c>
+      <c r="D83" s="68" t="inlineStr">
+        <is>
+          <t>US leads 7.5-8x in both training and inference</t>
+        </is>
+      </c>
+      <c r="E83" s="69" t="inlineStr">
+        <is>
+          <t>2035E</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Gap narrows further to ~8:1 but never closes; EU's strategy must be efficiency + sovereignty not scale parity</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
           <t>ASSESSMENT</t>
         </is>
       </c>
-      <c r="B54" s="58" t="inlineStr">
+    </row>
+    <row r="85" ht="65" customHeight="1">
+      <c r="A85" s="70" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B85" s="70" t="inlineStr">
+        <is>
+          <t>Overall Verdict</t>
+        </is>
+      </c>
+      <c r="C85" s="71" t="inlineStr">
+        <is>
+          <t>EU AI Gigafactory programme is necessary but not sufficient for LLM leadership</t>
+        </is>
+      </c>
+      <c r="D85" s="72" t="inlineStr"/>
+      <c r="E85" s="73" t="inlineStr">
+        <is>
+          <t>2030-2035</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>EU will not match US compute scale; goal should be 'strategic autonomy' not 'parity'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="65" customHeight="1">
+      <c r="A86" s="70" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B86" s="70" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="C86" s="71" t="inlineStr">
+        <is>
+          <t>Largest public AI infrastructure programme globally; strong private interest (76 bids); sovereign compute for EU-critical applications; open-source ecosystem (Mistral, Hugging Face); multilingual data advantage</t>
+        </is>
+      </c>
+      <c r="D86" s="72" t="inlineStr"/>
+      <c r="E86" s="73" t="inlineStr"/>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>These are genuine differentiators vs. US private-sector-dominated model</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="65" customHeight="1">
+      <c r="A87" s="70" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B87" s="70" t="inlineStr">
+        <is>
+          <t>Weaknesses</t>
+        </is>
+      </c>
+      <c r="C87" s="71" t="inlineStr">
+        <is>
+          <t>3-4 year deployment lag vs. US; 75K GPUs/facility may be outdated by arrival; procurement complexity; energy bottleneck; talent retention; no EU AI chip for initial deployment; single frontier model developer (Mistral)</t>
+        </is>
+      </c>
+      <c r="D87" s="72" t="inlineStr"/>
+      <c r="E87" s="73" t="inlineStr"/>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Speed of execution is the make-or-break factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="65" customHeight="1">
+      <c r="A88" s="70" t="inlineStr">
+        <is>
+          <t>ASSESSMENT</t>
+        </is>
+      </c>
+      <c r="B88" s="70" t="inlineStr">
         <is>
           <t>Key Success Metrics by 2035</t>
         </is>
       </c>
-      <c r="C54" s="59" t="inlineStr">
+      <c r="C88" s="71" t="inlineStr">
         <is>
           <t>(1) 7-8 Gigafactories operational with current-gen hardware; (2) 2+ EU frontier LLM developers; (3) 35-40% of EU enterprise LLM market served by EU models; (4) 10-15% of Gigafactory GPUs EU-designed; (5) EU LLM used in all 27 Member State governments</t>
         </is>
       </c>
-      <c r="D54" s="60" t="inlineStr"/>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="D88" s="72" t="inlineStr"/>
+      <c r="E88" s="73" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
         <is>
           <t>If all 5 metrics met, EU achieves meaningful LLM sovereignty; if &lt;3, programme has underdelivered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F54"/>
-  <mergeCells count="7">
+  <autoFilter ref="A1:F88"/>
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
